--- a/src/test/resources/TestDriver/Hearst_GHK/ActivityData/GHK_PSD_20260228.xlsx
+++ b/src/test/resources/TestDriver/Hearst_GHK/ActivityData/GHK_PSD_20260228.xlsx
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,10 +50,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,6 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,10 +472,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B2" s="1" t="n">
+      <c r="A2" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,7 +503,7 @@
           <t>GHK_954_2374839567_2602400003717</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I2" t="n">
@@ -508,10 +511,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="A3" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +542,7 @@
           <t>GHK_954_1335122501_2602400003530</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I3" t="n">
@@ -547,10 +550,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="A4" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,7 +581,7 @@
           <t>GHK_954_2246375808_2602400005617</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I4" t="n">
@@ -586,10 +589,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B5" s="1" t="n">
+      <c r="A5" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -617,7 +620,7 @@
           <t>GHK_954_0613348648_2602401003709</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I5" t="n">
@@ -625,10 +628,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B6" s="1" t="n">
+      <c r="A6" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,7 +659,7 @@
           <t>GHK_954_2490872880_2602400003550</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I6" t="n">
@@ -664,10 +667,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B7" s="1" t="n">
+      <c r="A7" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -695,7 +698,7 @@
           <t>GHK_954_2490872898_2602400003238</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I7" t="n">
@@ -703,10 +706,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B8" s="1" t="n">
+      <c r="A8" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -734,7 +737,7 @@
           <t>GHK_954_2490874712_2602400003340</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I8" t="n">
@@ -742,10 +745,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B9" s="1" t="n">
+      <c r="A9" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -773,7 +776,7 @@
           <t>GHK_954_0236356325_2602400005736</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I9" t="n">
@@ -781,10 +784,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B10" s="1" t="n">
+      <c r="A10" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -812,7 +815,7 @@
           <t>GHK_954_2420830735_2602400003226</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I10" t="n">
@@ -820,10 +823,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B11" s="1" t="n">
+      <c r="A11" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -851,7 +854,7 @@
           <t>GHK_954_2490875016_2602400005452</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I11" t="n">
@@ -859,10 +862,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B12" s="1" t="n">
+      <c r="A12" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -890,7 +893,7 @@
           <t>GHK_954_2393750928_2602401003509</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I12" t="n">
@@ -898,10 +901,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B13" s="1" t="n">
+      <c r="A13" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -929,7 +932,7 @@
           <t>GHK_954_1118150083_2602400003853</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I13" t="n">
@@ -937,10 +940,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B14" s="1" t="n">
+      <c r="A14" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -968,7 +971,7 @@
           <t>GHK_954_2405123601_2602400003718</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I14" t="n">
@@ -976,10 +979,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B15" s="1" t="n">
+      <c r="A15" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>GHK_954_0258330976_2602401003503</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I15" t="n">
@@ -1015,10 +1018,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B16" s="1" t="n">
+      <c r="A16" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1046,7 +1049,7 @@
           <t>GHK_954_1610451500_2602400003524</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I16" t="n">
@@ -1054,10 +1057,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B17" s="1" t="n">
+      <c r="A17" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B17" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1085,7 +1088,7 @@
           <t>GHK_954_2490880404_2602400004154</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I17" t="n">
@@ -1093,10 +1096,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B18" s="1" t="n">
+      <c r="A18" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B18" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1124,7 +1127,7 @@
           <t>GHK_954_2490880776_2602400002941</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I18" t="n">
@@ -1132,10 +1135,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B19" s="1" t="n">
+      <c r="A19" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B19" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1163,7 +1166,7 @@
           <t>GHK_954_2490883713_2602400003812</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I19" t="n">
@@ -1171,10 +1174,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B20" s="1" t="n">
+      <c r="A20" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B20" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1202,7 +1205,7 @@
           <t>GHK_954_2365682091_2602400003644</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I20" t="n">
@@ -1210,10 +1213,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B21" s="1" t="n">
+      <c r="A21" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B21" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1241,7 +1244,7 @@
           <t>GHK_954_2490883903_2602401003106</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I21" t="n">
@@ -1249,10 +1252,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B22" s="1" t="n">
+      <c r="A22" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B22" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1280,7 +1283,7 @@
           <t>GHK_954_1597054673_2602402003028</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I22" t="n">
@@ -1288,10 +1291,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B23" s="1" t="n">
+      <c r="A23" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1319,7 +1322,7 @@
           <t>GHK_954_2490885296_2602400003248</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I23" t="n">
@@ -1327,10 +1330,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B24" s="1" t="n">
+      <c r="A24" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B24" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1358,7 +1361,7 @@
           <t>GHK_954_2490891856_2602400003317</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I24" t="n">
@@ -1366,10 +1369,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B25" s="1" t="n">
+      <c r="A25" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B25" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1397,7 +1400,7 @@
           <t>GHK_954_2490891930_2602400003147</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I25" t="n">
@@ -1405,10 +1408,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B26" s="1" t="n">
+      <c r="A26" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B26" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1436,7 +1439,7 @@
           <t>GHK_954_2490897853_2602400003134</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I26" t="n">
@@ -1444,10 +1447,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B27" s="1" t="n">
+      <c r="A27" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B27" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1475,7 +1478,7 @@
           <t>GHK_954_2140189131_2602401003936</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I27" t="n">
@@ -1483,10 +1486,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B28" s="1" t="n">
+      <c r="A28" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B28" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1514,7 +1517,7 @@
           <t>GHK_954_2121332403_2602400010106</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I28" t="n">
@@ -1522,10 +1525,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B29" s="1" t="n">
+      <c r="A29" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B29" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1553,7 +1556,7 @@
           <t>GHK_954_2490923493_2602400003612</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I29" t="n">
@@ -1561,10 +1564,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B30" s="1" t="n">
+      <c r="A30" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B30" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1592,7 +1595,7 @@
           <t>GHK_954_1473587549_2602411003700</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I30" t="n">
@@ -1600,10 +1603,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B31" s="1" t="n">
+      <c r="A31" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B31" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1631,7 +1634,7 @@
           <t>GHK_954_2040004927_2602400003451</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I31" t="n">
@@ -1639,10 +1642,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B32" s="1" t="n">
+      <c r="A32" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B32" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1670,7 +1673,7 @@
           <t>GHK_954_1450663222_2602401002950</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I32" t="n">
@@ -1678,10 +1681,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B33" s="1" t="n">
+      <c r="A33" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B33" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1709,7 +1712,7 @@
           <t>GHK_954_2490906290_2602400003942</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I33" t="n">
@@ -1717,10 +1720,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B34" s="1" t="n">
+      <c r="A34" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B34" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1748,7 +1751,7 @@
           <t>GHK_954_2478277631_2602400010058</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I34" t="n">
@@ -1756,10 +1759,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B35" s="1" t="n">
+      <c r="A35" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B35" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1787,7 +1790,7 @@
           <t>GHK_954_1611036466_2602400003802</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I35" t="n">
@@ -1795,10 +1798,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B36" s="1" t="n">
+      <c r="A36" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B36" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1826,7 +1829,7 @@
           <t>GHK_954_0516356607_2602400010137</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I36" t="n">
@@ -1834,10 +1837,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B37" s="1" t="n">
+      <c r="A37" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -1865,7 +1868,7 @@
           <t>GHK_954_0266419803_2602400005720</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I37" t="n">
@@ -1873,10 +1876,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B38" s="1" t="n">
+      <c r="A38" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B38" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -1904,7 +1907,7 @@
           <t>GHK_954_1309259594_2602400003155</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I38" t="n">
@@ -1912,10 +1915,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B39" s="1" t="n">
+      <c r="A39" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B39" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -1943,7 +1946,7 @@
           <t>GHK_954_2490916190_2602400003231</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I39" t="n">
@@ -1951,10 +1954,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B40" s="1" t="n">
+      <c r="A40" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B40" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -1982,7 +1985,7 @@
           <t>GHK_954_2216273819_2602400003213</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I40" t="n">
@@ -1990,10 +1993,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B41" s="1" t="n">
+      <c r="A41" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B41" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2021,7 +2024,7 @@
           <t>GHK_954_2397869617_2602400003351</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I41" t="n">
@@ -2029,10 +2032,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B42" s="1" t="n">
+      <c r="A42" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B42" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2060,7 +2063,7 @@
           <t>GHK_954_2490916257_2602400003336</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I42" t="n">
@@ -2068,10 +2071,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B43" s="1" t="n">
+      <c r="A43" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B43" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2099,7 +2102,7 @@
           <t>GHK_954_2106265669_2602400003744</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I43" t="n">
@@ -2107,10 +2110,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B44" s="1" t="n">
+      <c r="A44" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B44" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2138,7 +2141,7 @@
           <t>GHK_954_1498795614_2602500002923</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I44" t="n">
@@ -2146,10 +2149,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B45" s="1" t="n">
+      <c r="A45" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B45" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2177,7 +2180,7 @@
           <t>GHK_954_0001803428_2602500004400</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I45" t="n">
@@ -2185,10 +2188,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B46" s="1" t="n">
+      <c r="A46" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B46" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2216,7 +2219,7 @@
           <t>GHK_954_2490916802_2602500004116</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I46" t="n">
@@ -2224,10 +2227,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B47" s="1" t="n">
+      <c r="A47" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B47" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2255,7 +2258,7 @@
           <t>GHK_954_1494291121_2602500003348</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I47" t="n">
@@ -2263,10 +2266,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B48" s="1" t="n">
+      <c r="A48" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B48" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2294,7 +2297,7 @@
           <t>GHK_954_2096010224_2602500003049</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I48" t="n">
@@ -2302,10 +2305,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B49" s="1" t="n">
+      <c r="A49" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B49" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2333,7 +2336,7 @@
           <t>GHK_954_2087945891_2602500003638</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I49" t="n">
@@ -2341,10 +2344,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B50" s="1" t="n">
+      <c r="A50" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B50" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -2372,7 +2375,7 @@
           <t>GHK_954_1562660041_2602500003955</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I50" t="n">
@@ -2380,10 +2383,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B51" s="1" t="n">
+      <c r="A51" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B51" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -2411,7 +2414,7 @@
           <t>GHK_954_2490917339_2602500003106</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I51" t="n">
@@ -2419,10 +2422,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B52" s="1" t="n">
+      <c r="A52" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B52" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -2450,7 +2453,7 @@
           <t>GHK_954_1418972681_2602500002649</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I52" t="n">
@@ -2458,10 +2461,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B53" s="1" t="n">
+      <c r="A53" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B53" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -2489,7 +2492,7 @@
           <t>GHK_954_2490917487_2602500003450</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I53" t="n">
@@ -2497,10 +2500,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B54" s="1" t="n">
+      <c r="A54" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B54" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -2528,7 +2531,7 @@
           <t>GHK_954_2490917685_2602500004245</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I54" t="n">
@@ -2536,10 +2539,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B55" s="1" t="n">
+      <c r="A55" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B55" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2567,7 +2570,7 @@
           <t>GHK_954_0646341404_2602500003415</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I55" t="n">
@@ -2575,10 +2578,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B56" s="1" t="n">
+      <c r="A56" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B56" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -2606,7 +2609,7 @@
           <t>GHK_954_1096763113_2602500003522</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I56" t="n">
@@ -2614,10 +2617,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B57" s="1" t="n">
+      <c r="A57" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B57" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -2645,7 +2648,7 @@
           <t>GHK_954_2490918030_2602500003330</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I57" t="n">
@@ -2653,10 +2656,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B58" s="1" t="n">
+      <c r="A58" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B58" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -2684,7 +2687,7 @@
           <t>GHK_954_2367634751_2602500004911</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I58" t="n">
@@ -2692,10 +2695,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B59" s="1" t="n">
+      <c r="A59" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B59" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -2723,7 +2726,7 @@
           <t>GHK_954_2328564790_2602500003751</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I59" t="n">
@@ -2731,10 +2734,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B60" s="1" t="n">
+      <c r="A60" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B60" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -2762,7 +2765,7 @@
           <t>GHK_954_2490924640_2602500004119</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I60" t="n">
@@ -2770,10 +2773,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B61" s="1" t="n">
+      <c r="A61" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B61" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -2801,7 +2804,7 @@
           <t>GHK_954_2490918279_2602501002646</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I61" t="n">
@@ -2809,10 +2812,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B62" s="1" t="n">
+      <c r="A62" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B62" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -2840,7 +2843,7 @@
           <t>GHK_954_2446766574_2602500004804</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I62" t="n">
@@ -2848,10 +2851,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B63" s="1" t="n">
+      <c r="A63" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B63" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -2879,7 +2882,7 @@
           <t>GHK_954_2274724885_2602500004301</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I63" t="n">
@@ -2887,10 +2890,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B64" s="1" t="n">
+      <c r="A64" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B64" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -2918,7 +2921,7 @@
           <t>GHK_954_2490918717_2602500003606</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I64" t="n">
@@ -2926,10 +2929,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B65" s="1" t="n">
+      <c r="A65" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B65" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -2957,7 +2960,7 @@
           <t>GHK_954_1210631378_2602500003324</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I65" t="n">
@@ -2965,10 +2968,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B66" s="1" t="n">
+      <c r="A66" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B66" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -2996,7 +2999,7 @@
           <t>GHK_954_2218689244_2602500004423</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I66" t="n">
@@ -3004,10 +3007,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B67" s="1" t="n">
+      <c r="A67" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B67" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -3035,7 +3038,7 @@
           <t>GHK_954_1330646892_2602500003321</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I67" t="n">
@@ -3043,10 +3046,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B68" s="1" t="n">
+      <c r="A68" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B68" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -3074,7 +3077,7 @@
           <t>GHK_954_2474692049_2602500003902</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I68" t="n">
@@ -3082,10 +3085,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B69" s="1" t="n">
+      <c r="A69" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B69" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -3113,7 +3116,7 @@
           <t>GHK_954_2490919855_2602500004515</t>
         </is>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I69" t="n">
@@ -3121,10 +3124,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B70" s="1" t="n">
+      <c r="A70" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B70" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -3152,7 +3155,7 @@
           <t>GHK_954_2333987762_2602500003812</t>
         </is>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I70" t="n">
@@ -3160,10 +3163,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B71" s="1" t="n">
+      <c r="A71" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B71" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -3191,7 +3194,7 @@
           <t>GHK_954_0228167664_2602500003748</t>
         </is>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I71" t="n">
@@ -3199,10 +3202,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B72" s="1" t="n">
+      <c r="A72" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B72" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -3230,7 +3233,7 @@
           <t>GHK_954_2490920473_2602500002929</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I72" t="n">
@@ -3238,10 +3241,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B73" s="1" t="n">
+      <c r="A73" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B73" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -3269,7 +3272,7 @@
           <t>GHK_954_2490924731_2602500004220</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I73" t="n">
@@ -3277,10 +3280,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B74" s="1" t="n">
+      <c r="A74" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B74" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -3308,7 +3311,7 @@
           <t>GHK_954_2374581680_2602500002827</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I74" t="n">
@@ -3316,10 +3319,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B75" s="1" t="n">
+      <c r="A75" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B75" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -3347,7 +3350,7 @@
           <t>GHK_954_0132605197_2602500005122</t>
         </is>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I75" t="n">
@@ -3355,10 +3358,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B76" s="1" t="n">
+      <c r="A76" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B76" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -3386,7 +3389,7 @@
           <t>GHK_954_0522542679_2602500003011</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I76" t="n">
@@ -3394,10 +3397,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B77" s="1" t="n">
+      <c r="A77" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B77" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -3425,7 +3428,7 @@
           <t>GHK_954_2490921141_2602500004549</t>
         </is>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I77" t="n">
@@ -3433,10 +3436,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B78" s="1" t="n">
+      <c r="A78" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B78" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -3464,7 +3467,7 @@
           <t>GHK_954_0895286797_2602500003101</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I78" t="n">
@@ -3472,10 +3475,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B79" s="1" t="n">
+      <c r="A79" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B79" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -3503,7 +3506,7 @@
           <t>GHK_954_1089406381_2602500003254</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I79" t="n">
@@ -3511,10 +3514,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B80" s="1" t="n">
+      <c r="A80" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B80" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -3542,7 +3545,7 @@
           <t>GHK_954_2490921604_2602600005018</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I80" t="n">
@@ -3550,10 +3553,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B81" s="1" t="n">
+      <c r="A81" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B81" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -3581,7 +3584,7 @@
           <t>GHK_954_2490921612_2602600002826</t>
         </is>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I81" t="n">
@@ -3589,10 +3592,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B82" s="1" t="n">
+      <c r="A82" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B82" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -3620,7 +3623,7 @@
           <t>GHK_954_2490922057_2602600003032</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I82" t="n">
@@ -3628,10 +3631,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B83" s="1" t="n">
+      <c r="A83" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B83" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -3659,7 +3662,7 @@
           <t>GHK_954_2490922206_2602600004522</t>
         </is>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I83" t="n">
@@ -3667,10 +3670,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B84" s="1" t="n">
+      <c r="A84" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B84" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -3698,7 +3701,7 @@
           <t>GHK_954_2361695907_2602600004914</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I84" t="n">
@@ -3706,10 +3709,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B85" s="1" t="n">
+      <c r="A85" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B85" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -3737,7 +3740,7 @@
           <t>GHK_954_2490924806_2602600002958</t>
         </is>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I85" t="n">
@@ -3745,10 +3748,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B86" s="1" t="n">
+      <c r="A86" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B86" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -3776,7 +3779,7 @@
           <t>GHK_954_2066759602_2602600003433</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I86" t="n">
@@ -3784,10 +3787,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B87" s="1" t="n">
+      <c r="A87" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B87" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -3815,7 +3818,7 @@
           <t>GHK_954_2490925076_2602601002629</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I87" t="n">
@@ -3823,10 +3826,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B88" s="1" t="n">
+      <c r="A88" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B88" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -3854,7 +3857,7 @@
           <t>GHK_954_0438578098_2602600004459</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I88" t="n">
@@ -3862,10 +3865,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B89" s="1" t="n">
+      <c r="A89" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B89" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -3893,7 +3896,7 @@
           <t>GHK_954_0917775058_2602600005037</t>
         </is>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I89" t="n">
@@ -3901,10 +3904,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B90" s="1" t="n">
+      <c r="A90" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B90" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -3932,7 +3935,7 @@
           <t>GHK_954_2407063557_2602600002833</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I90" t="n">
@@ -3940,10 +3943,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B91" s="1" t="n">
+      <c r="A91" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B91" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -3971,7 +3974,7 @@
           <t>GHK_954_2404179059_2602600003040</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I91" t="n">
@@ -3979,10 +3982,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B92" s="1" t="n">
+      <c r="A92" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B92" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -4010,7 +4013,7 @@
           <t>GHK_954_1596457737_2602600005156</t>
         </is>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I92" t="n">
@@ -4018,10 +4021,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B93" s="1" t="n">
+      <c r="A93" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B93" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -4049,7 +4052,7 @@
           <t>GHK_954_1560374918_2602600004104</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H93" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I93" t="n">
@@ -4057,10 +4060,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B94" s="1" t="n">
+      <c r="A94" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B94" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -4088,7 +4091,7 @@
           <t>GHK_954_2490925589_2602600002721</t>
         </is>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I94" t="n">
@@ -4096,10 +4099,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B95" s="1" t="n">
+      <c r="A95" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B95" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -4127,7 +4130,7 @@
           <t>GHK_954_0249510736_2602600003426</t>
         </is>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="H95" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I95" t="n">
@@ -4135,10 +4138,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B96" s="1" t="n">
+      <c r="A96" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B96" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -4166,7 +4169,7 @@
           <t>GHK_954_2490925738_2602600003340</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I96" t="n">
@@ -4174,10 +4177,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B97" s="1" t="n">
+      <c r="A97" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B97" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -4205,7 +4208,7 @@
           <t>GHK_954_1316696036_2602600004828</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I97" t="n">
@@ -4213,10 +4216,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B98" s="1" t="n">
+      <c r="A98" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B98" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -4244,7 +4247,7 @@
           <t>GHK_954_2473856439_2602602002738</t>
         </is>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I98" t="n">
@@ -4252,10 +4255,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B99" s="1" t="n">
+      <c r="A99" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B99" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -4283,7 +4286,7 @@
           <t>GHK_954_2304767706_2602600004001</t>
         </is>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I99" t="n">
@@ -4291,10 +4294,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B100" s="1" t="n">
+      <c r="A100" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B100" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -4322,7 +4325,7 @@
           <t>GHK_954_2490932437_2602600004849</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I100" t="n">
@@ -4330,10 +4333,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B101" s="1" t="n">
+      <c r="A101" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B101" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -4361,7 +4364,7 @@
           <t>GHK_954_2470145109_2602600003118</t>
         </is>
       </c>
-      <c r="H101" s="2" t="n">
+      <c r="H101" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I101" t="n">
@@ -4369,10 +4372,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B102" s="1" t="n">
+      <c r="A102" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B102" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -4400,7 +4403,7 @@
           <t>GHK_954_2070323148_2602600003701</t>
         </is>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I102" t="n">
@@ -4408,10 +4411,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B103" s="1" t="n">
+      <c r="A103" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B103" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -4439,7 +4442,7 @@
           <t>GHK_954_1530815719_2602600003419</t>
         </is>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H103" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I103" t="n">
@@ -4447,10 +4450,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B104" s="1" t="n">
+      <c r="A104" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B104" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -4478,7 +4481,7 @@
           <t>GHK_954_0225595867_2602600002657</t>
         </is>
       </c>
-      <c r="H104" s="2" t="n">
+      <c r="H104" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I104" t="n">
@@ -4486,10 +4489,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B105" s="1" t="n">
+      <c r="A105" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B105" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -4517,7 +4520,7 @@
           <t>GHK_954_2469178939_2602600004409</t>
         </is>
       </c>
-      <c r="H105" s="2" t="n">
+      <c r="H105" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I105" t="n">
@@ -4525,10 +4528,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B106" s="1" t="n">
+      <c r="A106" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B106" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -4556,7 +4559,7 @@
           <t>GHK_954_2490926959_2602600003927</t>
         </is>
       </c>
-      <c r="H106" s="2" t="n">
+      <c r="H106" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I106" t="n">
@@ -4564,10 +4567,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B107" s="1" t="n">
+      <c r="A107" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B107" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -4595,7 +4598,7 @@
           <t>GHK_954_1030021164_2602600003912</t>
         </is>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="H107" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I107" t="n">
@@ -4603,10 +4606,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B108" s="1" t="n">
+      <c r="A108" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B108" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -4634,7 +4637,7 @@
           <t>GHK_954_2130690056_2602600005207</t>
         </is>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="H108" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I108" t="n">
@@ -4642,10 +4645,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B109" s="1" t="n">
+      <c r="A109" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B109" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -4673,7 +4676,7 @@
           <t>GHK_954_1469620288_2602600004219</t>
         </is>
       </c>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I109" t="n">
@@ -4681,10 +4684,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B110" s="1" t="n">
+      <c r="A110" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B110" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -4712,7 +4715,7 @@
           <t>GHK_954_2471373502_2602600003603</t>
         </is>
       </c>
-      <c r="H110" s="2" t="n">
+      <c r="H110" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I110" t="n">
@@ -4720,10 +4723,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B111" s="1" t="n">
+      <c r="A111" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B111" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -4751,7 +4754,7 @@
           <t>GHK_954_0891116006_2602600004122</t>
         </is>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="H111" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I111" t="n">
@@ -4759,10 +4762,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B112" s="1" t="n">
+      <c r="A112" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B112" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -4790,7 +4793,7 @@
           <t>GHK_954_2490927775_2602600004831</t>
         </is>
       </c>
-      <c r="H112" s="2" t="n">
+      <c r="H112" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I112" t="n">
@@ -4798,10 +4801,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B113" s="1" t="n">
+      <c r="A113" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B113" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -4829,7 +4832,7 @@
           <t>GHK_954_2490927791_2602600005034</t>
         </is>
       </c>
-      <c r="H113" s="2" t="n">
+      <c r="H113" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I113" t="n">
@@ -4837,10 +4840,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B114" s="1" t="n">
+      <c r="A114" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B114" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -4868,7 +4871,7 @@
           <t>GHK_954_2490927957_2602600003334</t>
         </is>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="H114" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I114" t="n">
@@ -4876,10 +4879,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B115" s="1" t="n">
+      <c r="A115" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B115" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -4907,7 +4910,7 @@
           <t>GHK_954_2490907793_2602600002901</t>
         </is>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="H115" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I115" t="n">
@@ -4915,10 +4918,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B116" s="1" t="n">
+      <c r="A116" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B116" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -4946,7 +4949,7 @@
           <t>GHK_954_2489349841_2602600003434</t>
         </is>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H116" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I116" t="n">
@@ -4954,10 +4957,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B117" s="1" t="n">
+      <c r="A117" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B117" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -4985,7 +4988,7 @@
           <t>GHK_954_2490928229_2602600003021</t>
         </is>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H117" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I117" t="n">
@@ -4993,10 +4996,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B118" s="1" t="n">
+      <c r="A118" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B118" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -5024,7 +5027,7 @@
           <t>GHK_954_2490928245_2602600002943</t>
         </is>
       </c>
-      <c r="H118" s="2" t="n">
+      <c r="H118" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I118" t="n">
@@ -5032,10 +5035,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B119" s="1" t="n">
+      <c r="A119" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B119" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -5063,7 +5066,7 @@
           <t>GHK_954_2490928278_2602600003848</t>
         </is>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="H119" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I119" t="n">
@@ -5071,10 +5074,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B120" s="1" t="n">
+      <c r="A120" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B120" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -5102,7 +5105,7 @@
           <t>GHK_954_2189816602_2602602002612</t>
         </is>
       </c>
-      <c r="H120" s="2" t="n">
+      <c r="H120" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I120" t="n">
@@ -5110,10 +5113,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B121" s="1" t="n">
+      <c r="A121" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B121" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -5141,7 +5144,7 @@
           <t>GHK_954_1053048482_2602600003057</t>
         </is>
       </c>
-      <c r="H121" s="2" t="n">
+      <c r="H121" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I121" t="n">
@@ -5149,10 +5152,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B122" s="1" t="n">
+      <c r="A122" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B122" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -5180,7 +5183,7 @@
           <t>GHK_954_2490928534_2602600003817</t>
         </is>
       </c>
-      <c r="H122" s="2" t="n">
+      <c r="H122" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I122" t="n">
@@ -5188,10 +5191,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B123" s="1" t="n">
+      <c r="A123" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B123" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -5219,7 +5222,7 @@
           <t>GHK_954_0508307949_2602601002614</t>
         </is>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="H123" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I123" t="n">
@@ -5227,10 +5230,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B124" s="1" t="n">
+      <c r="A124" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B124" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -5258,7 +5261,7 @@
           <t>GHK_954_0223189135_2602600005152</t>
         </is>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="H124" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I124" t="n">
@@ -5266,10 +5269,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B125" s="1" t="n">
+      <c r="A125" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B125" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -5297,7 +5300,7 @@
           <t>GHK_954_2490928765_2602600003706</t>
         </is>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="H125" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I125" t="n">
@@ -5305,10 +5308,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B126" s="1" t="n">
+      <c r="A126" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B126" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -5336,7 +5339,7 @@
           <t>GHK_954_2490928815_2602600003329</t>
         </is>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="H126" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I126" t="n">
@@ -5344,10 +5347,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B127" s="1" t="n">
+      <c r="A127" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B127" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -5375,7 +5378,7 @@
           <t>GHK_954_2490932502_2602600003842</t>
         </is>
       </c>
-      <c r="H127" s="2" t="n">
+      <c r="H127" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I127" t="n">
@@ -5383,10 +5386,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B128" s="1" t="n">
+      <c r="A128" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B128" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -5414,7 +5417,7 @@
           <t>GHK_954_2480718127_2602600003942</t>
         </is>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H128" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I128" t="n">
@@ -5422,10 +5425,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B129" s="1" t="n">
+      <c r="A129" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B129" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -5453,7 +5456,7 @@
           <t>GHK_954_2376594921_2602600004131</t>
         </is>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="H129" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I129" t="n">
@@ -5461,10 +5464,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B130" s="1" t="n">
+      <c r="A130" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B130" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -5492,7 +5495,7 @@
           <t>GHK_954_2490929615_2602600005050</t>
         </is>
       </c>
-      <c r="H130" s="2" t="n">
+      <c r="H130" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I130" t="n">
@@ -5500,10 +5503,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B131" s="1" t="n">
+      <c r="A131" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B131" s="3" t="n">
         <v>46028</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -5531,11 +5534,5627 @@
           <t>GHK_954_2490932510_2602600003614</t>
         </is>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H131" s="4" t="n">
         <v>0.1667</v>
       </c>
       <c r="I131" t="n">
         <v>82387</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>169tZbV95eLRI2qY-986321</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>li_Qw6RI7zCv9mo0JNO</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_12_Print</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>GHK_954_2075117560_2602300130742</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I132" t="n">
+        <v>118214</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>169tZbV9FYLn56P8L-994382</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>li_FdvOxz906heAMXFr</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>GHK_954_2282359633_2602400132233</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I133" t="n">
+        <v>118223</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>169tZbV9KRd5v95uj-997649</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>li_BDN1SInZU8whul46</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_12_Print</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>GHK_954_2459917239_2602501093237</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I134" t="n">
+        <v>118228</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>169tZbV9L6pUN9Y3s-997822</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>li_nEoI13uG6EaIbQig</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709528_2602500121502</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I135" t="n">
+        <v>118233</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>169tZbV9O6uF1BH2t-1000921</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>li_HFVPPSDdsvi3EgCb</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>GHK_954_2471771812_2602600011329</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I136" t="n">
+        <v>118239</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>169wAkV99Ikxx2YiU-990208</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>li_TdL4wUpbN7H7ZvS9</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>GHK_954_2518697038_2602300114305</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I137" t="n">
+        <v>118647</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>169wAkV9ABiT93DCV-990364</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>li_mys9mJSIJYnp6DCb</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>GHK_954_2518699455_2602300152246</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I138" t="n">
+        <v>118652</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>169wAkV9BuN8N4Axa-990570</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>li_T3pUFlz5LNLJ9sV9</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>GHK_954_2518703695_2602300222737</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I139" t="n">
+        <v>118657</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>169wAkV9EazBK5mNF-994156</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>li_PP98Iv5IC0VoJcci</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>GHK_954_0923041552_2602500133102</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I140" t="n">
+        <v>118662</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>169wAkV9FLut76Gnu-994337</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>li_8vxWqJmOJoUhr3i0</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>GHK_954_2518705617_2602400123302</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I141" t="n">
+        <v>118667</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>169wAkV9GPZuU6t71-994562</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>li_HroQXuYINqKHoEWL</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709932_2602500133142</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I142" t="n">
+        <v>118672</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>169wAkV9KADJ98syN-997587</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>li_YDqhD8s2mmigs075</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>GHK_954_0990356008_2602500082031</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I143" t="n">
+        <v>118677</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>169wAkV9Kiwr39Gwh-997721</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>li_Q6fRXUW7yMOH7Fvz</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>GHK_954_2518708884_2602500103744</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I144" t="n">
+        <v>118682</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>169wAkV9MHQe3AFtV-998103</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>li_crQJP4p9RLX5YlRQ</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>GHK_954_2518716879_2602500170239</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I145" t="n">
+        <v>118687</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>16BZ33V93tPdo2tJI-986055</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>li_SrvsYT7mTyrxXBBZ</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>GHK_954_2518697467_2602300130619</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I146" t="n">
+        <v>122969</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>16CJ9QV9Avfym3fpD-990469</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>li_pdMVJ017c2CCzE27</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>GHK_954_2518703299_2602300182249</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I147" t="n">
+        <v>126080</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>16CJ9QV9BMIgk3unq-990520</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>li_w1Yz0BCry56lprwx</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>GHK_954_2263355352_2602300201244</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I148" t="n">
+        <v>126087</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>16CJ9QV9E0UkR5MQn-994044</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>li_jjyPy6TPcov14kih</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>GHK_954_2518703976_2602400070334</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I149" t="n">
+        <v>126092</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>16CJ9QV9FReXr6Jo2-994352</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>li_rb81641qiS1vQRBj</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>GHK_954_0226411544_2602400125741</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I150" t="n">
+        <v>126097</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>16CJ9QV9FptI26Yue-994455</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>li_GHOzJpHm5afF4u2S</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706177_2602400143236</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I151" t="n">
+        <v>126102</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>16CJ9QV9LLE4U9h3V-997891</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>li_78J6zcC9t6fIaDEq</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709742_2602500130750</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I152" t="n">
+        <v>126107</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>16CJ9QV9N2qPqAhq2-998217</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>li_DGyMLHnNXDi9ZLBb</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>GHK_954_2389980802_2602500200745</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I153" t="n">
+        <v>126112</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>16CLckV9A2WDN384d-990338</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>li_rofIo33UNbGV30sj</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>GHK_954_2518698937_2602300144733</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I154" t="n">
+        <v>126871</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>16CLckV9FVras6NGw-994367</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>li_YWpKRunrvKDeO2gz</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>GHK_954_0232157404_2602401131256</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I155" t="n">
+        <v>126876</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>16CLckV9FWDZQ6NVd-994371</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>li_apwKrerXRsEmmQVI</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>GHK_954_1294813751_2602400131302</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I156" t="n">
+        <v>126881</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>16CLckV9Fkda06WMp-994427</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>li_BkfY6zuWuQJ3gkwO</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706078_2602400141345</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I157" t="n">
+        <v>126886</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>16CLckV9Fmpun6XtU-994437</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>li_QcLbeWVA0zWufGBx</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>GHK_954_1594092023_2602500133125</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I158" t="n">
+        <v>126891</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>16CLckV9FzQns6fCu-994483</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>li_X7ARPhzwPNkKDs4P</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706334_2602400151239</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I159" t="n">
+        <v>126896</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>16CLckV9LZNAr9qXY-997942</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>li_ZP6E9MR2WJ775lGP</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>GHK_954_2472424239_2602500140737</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I160" t="n">
+        <v>126901</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>16CLckV9M9TRWAD1k-998076</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>li_ebqLYTP3iO5Cl40e</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>GHK_954_2179710385_2602601111805</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I161" t="n">
+        <v>126906</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>16CLckV9RDrVMDboT-1001267</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>li_TNb7kRlwLaj45yK6</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>GHK_954_2518730904_2602600131811</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I162" t="n">
+        <v>126911</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>16CXVNV99W64s2jY8-990241</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>li_yZgXjs9OliZFN4o7</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>GHK_954_2518697293_2602300123751</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I163" t="n">
+        <v>128964</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>16CXVNV9Aw80T3fQ1-990470</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>li_633EhROfX0Q4IIsZ</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>GHK_954_2389728730_2602300182738</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I164" t="n">
+        <v>128969</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>16CXVNV9Kx4gd9QVv-997780</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>li_VZ3GDqdOlgdw6ZaT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709304_2602500113242</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I165" t="n">
+        <v>128976</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>16CXVNV9L8w5H9YbS-997836</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>li_3osSR6FHXOOgTUfw</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>GHK_954_1574973929_2602502133241</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I166" t="n">
+        <v>128981</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>16CXVNV9LIDje9eTl-997876</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>li_1bbUFEdFxKWpq1fL</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>GHK_954_2517341232_2602500125757</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I167" t="n">
+        <v>128986</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>16CXVNV9PhtoFCIDO-1000987</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>li_HHX62CEFrMsIDzrQ</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>GHK_954_2518717778_2602600070347</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I168" t="n">
+        <v>128991</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>16CXVNV9QLOsdCnsN-1001092</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>li_DcwXxahQUwgMV9fp</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>GHK_954_1119458501_2602601094238</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I169" t="n">
+        <v>128996</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>16CXVNV9QWvFQCy6N-1001141</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>li_pH1xL74GWa3XEjc3</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>GHK_954_2518720459_2602600102737</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I170" t="n">
+        <v>129001</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>16CXVNV9RvG3cE77z-1001382</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>li_XGTtlch0Ft4zSRdJ</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>GHK_954_2523931778_2602600160836</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I171" t="n">
+        <v>129006</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>16CcLDV9QouWpDHDy-1001199</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>li_VjKC2hP3IPcCyBru</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>GHK_954_2482233000_2602600113751</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I172" t="n">
+        <v>129842</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>16CcLDV9R4pWeDVGb-1001240</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>li_3PO2KzH0uH1utLjt</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_12_Print</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>GHK_954_2190047551_2602601124259</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I173" t="n">
+        <v>129847</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>16CcLDV9SHzkDEP5y-1001453</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>li_mHuKymY9MayNL4tw</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>GHK_954_2523936306_2602600173849</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I174" t="n">
+        <v>129852</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>6oZhlV9JxRpj8j7b-997549</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>li_nmEHa8NSBLAt97o7</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>GHK_954_0510371586_2602500072821</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I175" t="n">
+        <v>129938</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>6oZhlV9KFwOi8umO-997604</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>li_c0rLJJdQofbhZFOY</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>GHK_954_2518708298_2602500084306</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I176" t="n">
+        <v>129943</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>6oZhlV9KcVSf9ANk-997693</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>li_C38lf6pPR08ygcQn</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>GHK_954_0265070789_2602500101257</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I177" t="n">
+        <v>129948</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>6oZhlV9Ktcs49MYd-997765</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>li_7Fs3iH33SR9AnaHt</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>GHK_954_2426076192_2602500111740</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I178" t="n">
+        <v>129953</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>6oZhlV9Qvh3mDJkf-1001216</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>li_EGBBpt65K5tMLzIa</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>GHK_954_2490927767_2602610120449</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I179" t="n">
+        <v>129962</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>6oZhlV9SCUVVEID1-1001435</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>li_KUn0nkgWDi70S2pM</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>GHK_954_2057298560_2602600171750</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I180" t="n">
+        <v>129967</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>6oamnV96TYYvWbG-987720</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>li_Tz4JOTgrL3HQPm6z</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>GHK_954_1609037476_2602300130923</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I181" t="n">
+        <v>130232</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>6oamnV9ErQYQ5vgI-994228</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>li_2JFdF9aam7oCSeqW</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>GHK_954_2518704982_2602405103259</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I182" t="n">
+        <v>130240</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B183" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>6oamnV9FeQjY6Qzq-994409</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>li_B8ODIuFFaiz4wLTk</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>GHK_954_2518705922_2602400134736</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I183" t="n">
+        <v>130245</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B184" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>6oamnV9KHLp78wbf-997611</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>li_hLgJW8hiU0idgYZF</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>GHK_954_2518708306_2602500084757</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I184" t="n">
+        <v>130250</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>6oamnV9KyjZu9Ql0-997789</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>li_mMxrsZRYF7kPA8rY</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>GHK_954_0221816721_2602500113756</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I185" t="n">
+        <v>130260</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>6oamnV9NALb5Ak9d-998227</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>li_BIb7nIaLzxmh4Ubw</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>GHK_954_2250447022_2602500203737</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I186" t="n">
+        <v>130265</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>6oamnV9RqnoRE2k2-1001364</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>li_n82UoUrU5FYi117A</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>GHK_954_2451838292_2602600155245</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I187" t="n">
+        <v>130274</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>6opQjV9B5wg43lys-990490</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>li_PX7ICBqW43CxbXD9</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>GHK_954_2518703364_2602300190743</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I188" t="n">
+        <v>131384</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>6opQjV9Bdqff430M-990545</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>li_wEK0ZHKNXyzw0CvP</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>GHK_954_0266451301_2602300212242</t>
+        </is>
+      </c>
+      <c r="H189" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I189" t="n">
+        <v>131389</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>6opQjV9ERMnm5e7X-994116</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>li_otl7TBGyQibnSVJx</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>GHK_954_1436780512_2602400084755</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I190" t="n">
+        <v>131394</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>6opQjV9Fa30a6Odp-994387</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>li_OOVqDNfiacWGuWRH</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>GHK_954_2518705914_2602400134231</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I191" t="n">
+        <v>131399</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>6opQjV9FqzTC6YjG-994457</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>li_vEGeHtSJHsSvczpe</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706219_2602400143737</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I192" t="n">
+        <v>131406</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>6opQjV9Gjvih73R3-994617</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>li_3NthSdOx65UPbWeC</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>GHK_954_1102093026_2602500133152</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I193" t="n">
+        <v>131414</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>6opQjV9KKFCZ8xnW-997618</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>li_bTOk9HZy3mGy8sR5</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>GHK_954_2518708363_2602500085745</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I194" t="n">
+        <v>131419</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>6opQjV9OTRyCBQEu-1000935</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>li_ILNMYLUDEdzw1IkR</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>GHK_954_2490858426_2602600020251</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I195" t="n">
+        <v>131427</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>6opQjV9QidskD82i-1001182</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>li_Fe4fOwTPH2IQN59N</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>GHK_954_1289672519_2602600111252</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I196" t="n">
+        <v>131432</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AzZUMFV9GRAU06tEG-994571</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>li_w0OO31Fa4MPbUAnO</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706748_2602400170246</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I197" t="n">
+        <v>133934</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AzZUMFV9Gid44733K-994612</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>li_GYEIlhDpue9o9BTS</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706896_2602400181109</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I198" t="n">
+        <v>133939</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AzZUMFV9GsMsv798u-994640</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>li_6M0o4oNzxHMYICc6</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>GHK_954_1001118510_2602400184834</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I199" t="n">
+        <v>133944</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AzZUMFV9LKRBB9ekR-997887</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>li_FujhazkLCSetLoo2</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709726_2602500130748</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I200" t="n">
+        <v>133949</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B201" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AzZUMFV9PdbDoCEU5-1000978</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>li_8ZpnGeWJyFjTePc8</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>GHK_954_2079149114_2602600064751</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I201" t="n">
+        <v>133954</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AzZUMFV9QO724CpXI-1001107</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>li_08zs3X0xKkLaMp1R</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>GHK_954_1258694577_2602600095245</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I202" t="n">
+        <v>133959</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AzZf6IV9EUJLu5frb-994131</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>li_BI9syu59Mn7gvcU9</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>GHK_954_2492789330_2602400090255</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I203" t="n">
+        <v>136270</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AzZf6IV9Ff6fe6R2t-994412</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>li_12RFdoAdhcvsXv8o</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>GHK_954_1581823232_2602400135245</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I204" t="n">
+        <v>136277</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AzZf6IV9KUpSi94nw-997659</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>li_I3mNATCW4BxMzPNN</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>GHK_954_2452252899_2602500094315</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I205" t="n">
+        <v>136282</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>AzZf6IV9M4QYiA6bp-998061</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>li_RXcdAFDzQC80JgPr</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>GHK_954_2464450333_2602500160734</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I206" t="n">
+        <v>136287</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>AzZf6IV9MgZvSASkn-998170</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>li_ZYAtI5umY7ump25B</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>GHK_954_0271864837_2602600111813</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I207" t="n">
+        <v>136292</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>AzZf6IV9RNOxuDfRc-1001288</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>li_HCAnYg7z8YTGqP83</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>GHK_954_2523931125_2602600135853</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I208" t="n">
+        <v>136297</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>AzZf6IV9SHxznEKQt-1001452</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>li_KzBAvww6HBIOgILS</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>GHK_954_2523936314_2602600173850</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I209" t="n">
+        <v>136302</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AzZqtLV94pV4d3ZD5-986203</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>li_MTG0U436r9INJEVF</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>GHK_954_2130625029_2602300130651</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I210" t="n">
+        <v>138460</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Azq8UhV9FtcHK6atG-994463</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>li_sMZopQz5ITbr9sWc</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>GHK_954_0879978534_2602400144736</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I211" t="n">
+        <v>140152</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Azq8UhV9G65Qr6i7S-994502</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>li_hvTX4xeuvfIJDf0K</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709924_2602500133133</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I212" t="n">
+        <v>140157</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Azq8UhV9HH2bY7LzD-994695</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>li_OYFyFchgjJY8oPlP</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>GHK_954_2518707126_2602400202735</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I213" t="n">
+        <v>140162</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B214" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Azq8UhV9QAmaBCeme-1001059</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>li_Bt5Wu2uh9P731AdK</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>GHK_954_1435900632_2602600085745</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I214" t="n">
+        <v>140167</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Azq8UhV9QMNQVCovy-1001094</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>li_JIorZkvb6NYYuaXR</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>GHK_954_2412211142_2602600094242</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I215" t="n">
+        <v>140172</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Azq8UhV9Qzk2wDOc0-1001226</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>li_6nVboH8jnRF93ipK</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>GHK_954_0089706022_2602600122447</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I216" t="n">
+        <v>140177</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>AzqNGFV9F7klV67qH-994290</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>li_2BbI1HTg94eGrKC3</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>GHK_954_0162865125_2602400113739</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I217" t="n">
+        <v>143166</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>AzqNGFV9FAaBz69L6-994298</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>li_XiR0RuDYpEGG6xxw</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>GHK_954_1396496554_2602400114740</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I218" t="n">
+        <v>143171</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>AzqNGFV9JuzJE8kOR-997547</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>li_ZfRDGN8NEpy4ICpj</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>GHK_954_2518707761_2602500071738</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I219" t="n">
+        <v>143176</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>AzqNGFV9KnJhF9KLf-997737</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>li_SyEu0OKwXd1uNz7C</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>GHK_954_1227853650_2602500133231</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I220" t="n">
+        <v>143181</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AzqNGFV9Kr1lq9NFY-997752</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>li_BnjficBLSUeeYL4f</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>GHK_954_1097092629_2602500133232</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I221" t="n">
+        <v>143186</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AzqNGFV9L2BR79UUn-997804</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>li_4xV3BY5AyZRZSPMJ</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709403_2602500115246</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I222" t="n">
+        <v>143191</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>AzqNGFV9LdOzw9tPk-997953</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>li_a11APBOtzFx2Nup9</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>GHK_954_2518713504_2602500142241</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I223" t="n">
+        <v>143196</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>AzqNGFV9LvmTQA4fz-998020</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>li_ZDl6trIPMMYBMrOx</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>GHK_954_2490919863_2602500153246</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I224" t="n">
+        <v>143201</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>AzqNGFV9NVPjpAwS5-998273</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>li_SmRbbETeXDa58eej</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>GHK_954_2389695442_2602500220321</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I225" t="n">
+        <v>143206</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>AzqNGFV9QYGiqD0S2-1001148</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>li_7FBAYpqXEztb9PMv</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>GHK_954_1102031661_2602600103252</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I226" t="n">
+        <v>143211</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>AzqNGFV9RvMVLE7zu-1001383</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>li_a1gYlU85ETiFlYK7</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>GHK_954_1116475136_2602600160837</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I227" t="n">
+        <v>143220</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>AzqNcNV99O6oA2dFM-990223</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>li_ca8N6RDHBKq2yuQH</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>GHK_954_1305735985_2602300144220</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I228" t="n">
+        <v>143298</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>AzqNcNV9GdMxL70cC-994602</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>li_rPeBnAdo5plx1CL3</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709940_2602500133150</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I229" t="n">
+        <v>143303</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>AzqNcNV9K48pn8ohA-997558</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>li_J2ggPOJJC3hkYucj</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>GHK_954_1128982582_2602500133223</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I230" t="n">
+        <v>143308</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>AzqNcNV9QBqYfCglG-1001062</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>li_MiJ8j3ojKlSltnzd</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>GHK_954_0521566943_2602600090256</t>
+        </is>
+      </c>
+      <c r="H231" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I231" t="n">
+        <v>143313</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>AzqNcNV9QUXKWCxW2-1001130</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>li_OjrUJGlU3MTOc2Oo</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>GHK_954_1114312109_2602602101739</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I232" t="n">
+        <v>143318</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>AzqNcNV9RZzkPDt31-1001320</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>li_ioAPv5UJEK5OYvYa</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>GHK_954_1406975530_2602600144758</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I233" t="n">
+        <v>143323</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>AzqWeWV9AjnFb3XpU-990445</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>li_jQgPO1IQzKR4BGwY</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>GHK_954_0952093078_2602300173736</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I234" t="n">
+        <v>144641</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>AzqWeWV9FNz4y6Heo-994341</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>li_jQ6jWf3F7CbvlPsx</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>GHK_954_1237203862_2602500133117</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I235" t="n">
+        <v>144646</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>AzqWeWV9FzFM76eeB-994481</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>li_QuwyqxYDe1v9Y3pE</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706326_2602400151238</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I236" t="n">
+        <v>144651</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>AzqWeWV9KYdiS99O2-997675</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>li_w4rtJCWgqNMb2tbu</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>GHK_954_0607170875_2602500095737</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I237" t="n">
+        <v>144656</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>AzqWeWV9LsPEvA2A6-998008</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>li_MfpS9whMpJ9tl348</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>GHK_954_2518716580_2602501152239</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I238" t="n">
+        <v>144661</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>AzqWeWV9QR2EGCszK-1001120</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>li_NBl4emWXuKNIrQBc</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>GHK_954_2319668378_2602600100259</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I239" t="n">
+        <v>144666</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>AzqXD1V9GnLws77IG-994624</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>li_68pGGNRR87UX4tFR</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>GHK_954_1123778423_2602500133154</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I240" t="n">
+        <v>144811</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>AzqXD1V9Mop3vAakt-998194</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>li_GbGMwxY9LdUFUBzV</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_12_Print</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>GHK_954_1369490402_2602500192244</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I241" t="n">
+        <v>144816</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>AzqXD1V9RqOMSE4KP-1001362</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>li_0Pqk1r9JEQwKvgP4</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>GHK_954_0243086584_2602600155246</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I242" t="n">
+        <v>144821</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Azqe4YV9Ak2xR3Xd6-990446</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>li_ZwFtCh94B19cPChl</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>GHK_954_2472991344_2602300173738</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I243" t="n">
+        <v>146037</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Azqe4YV9CckTn4Wt6-994000</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>li_IXH81u5D66vCzQ5Z</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>GHK_954_2167868310_2602400012411</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I244" t="n">
+        <v>146042</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Azqe4YV9K8x1p8sSe-997577</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>li_u30Dcu4eOiXO993t</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>GHK_954_1036128484_2602500081543</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I245" t="n">
+        <v>146053</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Azqe4YV9KGVaW8xMo-997607</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>li_XIcQWbbmYSxVvoLp</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>GHK_954_2518708272_2602500084302</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I246" t="n">
+        <v>146058</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Azqe4YV9KbQcx9Bdw-997688</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>li_zxAuFsCXlIpbiaoG</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>GHK_954_1353465568_2602500100755</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I247" t="n">
+        <v>146063</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Azqe4YV9Lqj32A1Lz-998002</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>li_wejUDH2ERj2XRvwu</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>GHK_954_2509583171_2602500151240</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I248" t="n">
+        <v>146068</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Azqe4YV9LwLBvA4eH-998024</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>li_O0wfhmleLqyQzHfe</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>GHK_954_0915908693_2602600111804</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I249" t="n">
+        <v>146073</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Azqe4YV9NCeGnAmr9-998231</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>li_gYlWKqfZrdaPNrho</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>GHK_954_1324802428_2602500204742</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I250" t="n">
+        <v>146078</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Azqe4YV9QSq44Cuv3-1001127</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>li_IRaRxNUz9WwuyYPH</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>GHK_954_2518723206_2602601111828</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I251" t="n">
+        <v>146083</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>AzqfQNV9EXSsR5irO-994140</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>li_ygOjyN4G5i9ej2nC</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>GHK_954_2518704495_2602400091300</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I252" t="n">
+        <v>146465</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>AzqfQNV9F1gWV62p9-994264</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>li_errMfYj311NhCpgN</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>GHK_954_2518705252_2602400111252</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I253" t="n">
+        <v>146470</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>AzqfQNV9GO5ko6rSx-994557</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>li_ds328wDnF7V2MX11</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>GHK_954_1131290262_2602400164738</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I254" t="n">
+        <v>146475</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>AzqfQNV9KKqTj90T0-997620</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>li_PaiQeYmNYyeV5rB9</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>GHK_954_0444900773_2602500090309</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I255" t="n">
+        <v>146480</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>AzqfQNV9PbKhMCDi2-1000975</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>li_4XNDGBzzyAyj6mBt</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>GHK_954_2518717737_2602600063758</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I256" t="n">
+        <v>146485</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>AzqfQNV9Q8cX3CcuS-1001050</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>li_uL4iafPXRdFJ8GaT</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>GHK_954_1445842097_2602600085249</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I257" t="n">
+        <v>146494</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>AzqfQNV9RoFPJE2Go-1001355</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>li_IoDgooQwt5aM3RUw</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>GHK_954_2460597079_2602600154310</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I258" t="n">
+        <v>146503</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>AzqfQNV9RsgidE5KA-1001368</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>li_DVpodL3yQWcUHO9h</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>GHK_954_1535782252_2602600155753</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I259" t="n">
+        <v>146508</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>AzyXPPV92mQCt1yxB-985860</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>li_erKlHVAsYKtTV0fo</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>GHK_954_2518697459_2602300130536</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I260" t="n">
+        <v>147686</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Azyai8V941Qhu30DY-986079</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>li_5zMV3L9pJUilh3b7</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_12_Print</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>GHK_954_1506848454_2602300130624</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I261" t="n">
+        <v>148321</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>AzyckMV96mcPxhfV-989953</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>li_UPL0MBEVJ5Es6VSc</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>GHK_954_1019551090_2602300130951</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I262" t="n">
+        <v>148816</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>AzyckMV9FFjjR6CoN-994321</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>li_GR18rr8pDSBtbtJ5</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>GHK_954_2518705559_2602400121051</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I263" t="n">
+        <v>148836</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AzyckMV9GCZCw6loS-994527</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>li_hmcjQL8q0bOZhp4g</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>GHK_954_2518706540_2602400160241</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I264" t="n">
+        <v>148841</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>AzyckMV9LGd9h9dmh-997871</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>li_JOXqfsoJhaoFpCic</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>GHK_954_2518709643_2602500125239</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I265" t="n">
+        <v>148848</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>AzyckMV9LYvPj9pf1-997939</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>li_cHn3uhaVX9NUcJyb</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>GHK_954_0251949277_2602600111756</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I266" t="n">
+        <v>148856</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>AzyckMV9NBLQUAlTT-998229</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>li_L4DCP8vOvQgV4iQP</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>GHK_954_2384898306_2602500204239</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I267" t="n">
+        <v>148861</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>AzyckMV9OJD0sBMHd-1000931</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>li_XxTUxEnEaKLf0UVp</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>GHK_954_2518717596_2602600011909</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I268" t="n">
+        <v>148866</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>AzyckMV9Rm0wUE1WF-1001352</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>li_evJ2QaiCc7mPOy8V</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>GHK_954_1558908776_2602600153246</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I269" t="n">
+        <v>148871</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>AzyckMV9SKl2WEORl-1001463</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>li_GPYvKnTMuprtUokK</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>GHK_954_2518707464_2602600175249</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I270" t="n">
+        <v>148876</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AzyhzaV95mEQg7oi-986341</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>li_VASvaMh14vTU31ZW</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>GHK_954_0227981511_2602300130912</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I271" t="n">
+        <v>149927</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>AzyhzaV9BiCjx463B-990554</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>li_v2ZPFFlvzQy05Eq2</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>GHK_954_1561013580_2602500133047</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I272" t="n">
+        <v>149936</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AzyhzaV9FIz536GHH-994330</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>li_cj3Lp8u6zLPfNrXv</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>GHK_954_1075548345_2602400122240</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I273" t="n">
+        <v>149943</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>AzyhzaV9MtQl2AfBX-998197</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>li_9tQgdmxN2hElVaZ9</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_12_Print</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>GHK_954_2518717299_2602500193259</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I274" t="n">
+        <v>149948</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>AzyhzaV9Q9HxkCgin-1001052</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>li_wGEIjnkNYt79PrNj</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>GHK_PRTDIG_US_New_15_Print</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>GHK_954_2518719238_2602600085253</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I275" t="n">
+        <v>149957</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestDriver/Hearst_GHK/ActivityData/GHK_PSD_20260228.xlsx
+++ b/src/test/resources/TestDriver/Hearst_GHK/ActivityData/GHK_PSD_20260228.xlsx
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,12 +50,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +419,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,10 +469,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,7 +500,7 @@
           <t>GHK_954_2374839567_2602400003717</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I2" t="n">
@@ -511,10 +508,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,7 +539,7 @@
           <t>GHK_954_1335122501_2602400003530</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I3" t="n">
@@ -550,10 +547,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="A4" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -581,7 +578,7 @@
           <t>GHK_954_2246375808_2602400005617</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I4" t="n">
@@ -589,10 +586,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="A5" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -620,7 +617,7 @@
           <t>GHK_954_0613348648_2602401003709</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I5" t="n">
@@ -628,10 +625,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B6" s="3" t="n">
+      <c r="A6" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -659,7 +656,7 @@
           <t>GHK_954_2490872880_2602400003550</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I6" t="n">
@@ -667,10 +664,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="A7" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -698,7 +695,7 @@
           <t>GHK_954_2490872898_2602400003238</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I7" t="n">
@@ -706,10 +703,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B8" s="3" t="n">
+      <c r="A8" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -737,7 +734,7 @@
           <t>GHK_954_2490874712_2602400003340</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I8" t="n">
@@ -745,10 +742,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B9" s="3" t="n">
+      <c r="A9" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -776,7 +773,7 @@
           <t>GHK_954_0236356325_2602400005736</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I9" t="n">
@@ -784,10 +781,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B10" s="3" t="n">
+      <c r="A10" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -815,7 +812,7 @@
           <t>GHK_954_2420830735_2602400003226</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I10" t="n">
@@ -823,10 +820,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B11" s="3" t="n">
+      <c r="A11" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,7 +851,7 @@
           <t>GHK_954_2490875016_2602400005452</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I11" t="n">
@@ -862,10 +859,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B12" s="3" t="n">
+      <c r="A12" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -893,7 +890,7 @@
           <t>GHK_954_2393750928_2602401003509</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I12" t="n">
@@ -901,10 +898,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B13" s="3" t="n">
+      <c r="A13" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -932,7 +929,7 @@
           <t>GHK_954_1118150083_2602400003853</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I13" t="n">
@@ -940,10 +937,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B14" s="3" t="n">
+      <c r="A14" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -971,7 +968,7 @@
           <t>GHK_954_2405123601_2602400003718</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I14" t="n">
@@ -979,10 +976,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B15" s="3" t="n">
+      <c r="A15" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>GHK_954_0258330976_2602401003503</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I15" t="n">
@@ -1018,10 +1015,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B16" s="3" t="n">
+      <c r="A16" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B16" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1049,7 +1046,7 @@
           <t>GHK_954_1610451500_2602400003524</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I16" t="n">
@@ -1057,10 +1054,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B17" s="3" t="n">
+      <c r="A17" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1088,7 +1085,7 @@
           <t>GHK_954_2490880404_2602400004154</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I17" t="n">
@@ -1096,10 +1093,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B18" s="3" t="n">
+      <c r="A18" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1127,7 +1124,7 @@
           <t>GHK_954_2490880776_2602400002941</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I18" t="n">
@@ -1135,10 +1132,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B19" s="3" t="n">
+      <c r="A19" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1166,7 +1163,7 @@
           <t>GHK_954_2490883713_2602400003812</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I19" t="n">
@@ -1174,10 +1171,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B20" s="3" t="n">
+      <c r="A20" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B20" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1205,7 +1202,7 @@
           <t>GHK_954_2365682091_2602400003644</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I20" t="n">
@@ -1213,10 +1210,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B21" s="3" t="n">
+      <c r="A21" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1244,7 +1241,7 @@
           <t>GHK_954_2490883903_2602401003106</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I21" t="n">
@@ -1252,10 +1249,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B22" s="3" t="n">
+      <c r="A22" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B22" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1283,7 +1280,7 @@
           <t>GHK_954_1597054673_2602402003028</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I22" t="n">
@@ -1291,10 +1288,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B23" s="3" t="n">
+      <c r="A23" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B23" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1322,7 +1319,7 @@
           <t>GHK_954_2490885296_2602400003248</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I23" t="n">
@@ -1330,10 +1327,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B24" s="3" t="n">
+      <c r="A24" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B24" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1361,7 +1358,7 @@
           <t>GHK_954_2490891856_2602400003317</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I24" t="n">
@@ -1369,10 +1366,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B25" s="3" t="n">
+      <c r="A25" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B25" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1400,7 +1397,7 @@
           <t>GHK_954_2490891930_2602400003147</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I25" t="n">
@@ -1408,10 +1405,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B26" s="3" t="n">
+      <c r="A26" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B26" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1439,7 +1436,7 @@
           <t>GHK_954_2490897853_2602400003134</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I26" t="n">
@@ -1447,10 +1444,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B27" s="3" t="n">
+      <c r="A27" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B27" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1478,7 +1475,7 @@
           <t>GHK_954_2140189131_2602401003936</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I27" t="n">
@@ -1486,10 +1483,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B28" s="3" t="n">
+      <c r="A28" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B28" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1517,7 +1514,7 @@
           <t>GHK_954_2121332403_2602400010106</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I28" t="n">
@@ -1525,10 +1522,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B29" s="3" t="n">
+      <c r="A29" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B29" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1556,7 +1553,7 @@
           <t>GHK_954_2490923493_2602400003612</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I29" t="n">
@@ -1564,10 +1561,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B30" s="3" t="n">
+      <c r="A30" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B30" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1595,7 +1592,7 @@
           <t>GHK_954_1473587549_2602411003700</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I30" t="n">
@@ -1603,10 +1600,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B31" s="3" t="n">
+      <c r="A31" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B31" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1634,7 +1631,7 @@
           <t>GHK_954_2040004927_2602400003451</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I31" t="n">
@@ -1642,10 +1639,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B32" s="3" t="n">
+      <c r="A32" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B32" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1673,7 +1670,7 @@
           <t>GHK_954_1450663222_2602401002950</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I32" t="n">
@@ -1681,10 +1678,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B33" s="3" t="n">
+      <c r="A33" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B33" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1712,7 +1709,7 @@
           <t>GHK_954_2490906290_2602400003942</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I33" t="n">
@@ -1720,10 +1717,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B34" s="3" t="n">
+      <c r="A34" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B34" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1751,7 +1748,7 @@
           <t>GHK_954_2478277631_2602400010058</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I34" t="n">
@@ -1759,10 +1756,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B35" s="3" t="n">
+      <c r="A35" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B35" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1790,7 +1787,7 @@
           <t>GHK_954_1611036466_2602400003802</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I35" t="n">
@@ -1798,10 +1795,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B36" s="3" t="n">
+      <c r="A36" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B36" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1829,7 +1826,7 @@
           <t>GHK_954_0516356607_2602400010137</t>
         </is>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I36" t="n">
@@ -1837,10 +1834,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B37" s="3" t="n">
+      <c r="A37" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B37" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -1868,7 +1865,7 @@
           <t>GHK_954_0266419803_2602400005720</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I37" t="n">
@@ -1876,10 +1873,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B38" s="3" t="n">
+      <c r="A38" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B38" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -1907,7 +1904,7 @@
           <t>GHK_954_1309259594_2602400003155</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I38" t="n">
@@ -1915,10 +1912,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B39" s="3" t="n">
+      <c r="A39" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B39" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -1946,7 +1943,7 @@
           <t>GHK_954_2490916190_2602400003231</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I39" t="n">
@@ -1954,10 +1951,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B40" s="3" t="n">
+      <c r="A40" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B40" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -1985,7 +1982,7 @@
           <t>GHK_954_2216273819_2602400003213</t>
         </is>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I40" t="n">
@@ -1993,10 +1990,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B41" s="3" t="n">
+      <c r="A41" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B41" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2024,7 +2021,7 @@
           <t>GHK_954_2397869617_2602400003351</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I41" t="n">
@@ -2032,10 +2029,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B42" s="3" t="n">
+      <c r="A42" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B42" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2063,7 +2060,7 @@
           <t>GHK_954_2490916257_2602400003336</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I42" t="n">
@@ -2071,10 +2068,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B43" s="3" t="n">
+      <c r="A43" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B43" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2102,7 +2099,7 @@
           <t>GHK_954_2106265669_2602400003744</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I43" t="n">
@@ -2110,10 +2107,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B44" s="3" t="n">
+      <c r="A44" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B44" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2141,7 +2138,7 @@
           <t>GHK_954_1498795614_2602500002923</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I44" t="n">
@@ -2149,10 +2146,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B45" s="3" t="n">
+      <c r="A45" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B45" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2180,7 +2177,7 @@
           <t>GHK_954_0001803428_2602500004400</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I45" t="n">
@@ -2188,10 +2185,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B46" s="3" t="n">
+      <c r="A46" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B46" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2219,7 +2216,7 @@
           <t>GHK_954_2490916802_2602500004116</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H46" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I46" t="n">
@@ -2227,10 +2224,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B47" s="3" t="n">
+      <c r="A47" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B47" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2258,7 +2255,7 @@
           <t>GHK_954_1494291121_2602500003348</t>
         </is>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I47" t="n">
@@ -2266,10 +2263,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B48" s="3" t="n">
+      <c r="A48" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B48" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2297,7 +2294,7 @@
           <t>GHK_954_2096010224_2602500003049</t>
         </is>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="H48" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I48" t="n">
@@ -2305,10 +2302,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B49" s="3" t="n">
+      <c r="A49" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B49" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2336,7 +2333,7 @@
           <t>GHK_954_2087945891_2602500003638</t>
         </is>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I49" t="n">
@@ -2344,10 +2341,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B50" s="3" t="n">
+      <c r="A50" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B50" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -2375,7 +2372,7 @@
           <t>GHK_954_1562660041_2602500003955</t>
         </is>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I50" t="n">
@@ -2383,10 +2380,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B51" s="3" t="n">
+      <c r="A51" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B51" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -2414,7 +2411,7 @@
           <t>GHK_954_2490917339_2602500003106</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I51" t="n">
@@ -2422,10 +2419,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B52" s="3" t="n">
+      <c r="A52" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B52" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -2453,7 +2450,7 @@
           <t>GHK_954_1418972681_2602500002649</t>
         </is>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I52" t="n">
@@ -2461,10 +2458,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B53" s="3" t="n">
+      <c r="A53" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B53" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -2492,7 +2489,7 @@
           <t>GHK_954_2490917487_2602500003450</t>
         </is>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I53" t="n">
@@ -2500,10 +2497,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B54" s="3" t="n">
+      <c r="A54" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B54" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -2531,7 +2528,7 @@
           <t>GHK_954_2490917685_2602500004245</t>
         </is>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I54" t="n">
@@ -2539,10 +2536,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B55" s="3" t="n">
+      <c r="A55" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B55" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2570,7 +2567,7 @@
           <t>GHK_954_0646341404_2602500003415</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I55" t="n">
@@ -2578,10 +2575,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B56" s="3" t="n">
+      <c r="A56" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B56" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -2609,7 +2606,7 @@
           <t>GHK_954_1096763113_2602500003522</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I56" t="n">
@@ -2617,10 +2614,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B57" s="3" t="n">
+      <c r="A57" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B57" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -2648,7 +2645,7 @@
           <t>GHK_954_2490918030_2602500003330</t>
         </is>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I57" t="n">
@@ -2656,10 +2653,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B58" s="3" t="n">
+      <c r="A58" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B58" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -2687,7 +2684,7 @@
           <t>GHK_954_2367634751_2602500004911</t>
         </is>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I58" t="n">
@@ -2695,10 +2692,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B59" s="3" t="n">
+      <c r="A59" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B59" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -2726,7 +2723,7 @@
           <t>GHK_954_2328564790_2602500003751</t>
         </is>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I59" t="n">
@@ -2734,10 +2731,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B60" s="3" t="n">
+      <c r="A60" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B60" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -2765,7 +2762,7 @@
           <t>GHK_954_2490924640_2602500004119</t>
         </is>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I60" t="n">
@@ -2773,10 +2770,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B61" s="3" t="n">
+      <c r="A61" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B61" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -2804,7 +2801,7 @@
           <t>GHK_954_2490918279_2602501002646</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I61" t="n">
@@ -2812,10 +2809,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B62" s="3" t="n">
+      <c r="A62" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B62" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -2843,7 +2840,7 @@
           <t>GHK_954_2446766574_2602500004804</t>
         </is>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I62" t="n">
@@ -2851,10 +2848,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B63" s="3" t="n">
+      <c r="A63" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B63" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -2882,7 +2879,7 @@
           <t>GHK_954_2274724885_2602500004301</t>
         </is>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I63" t="n">
@@ -2890,10 +2887,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B64" s="3" t="n">
+      <c r="A64" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B64" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -2921,7 +2918,7 @@
           <t>GHK_954_2490918717_2602500003606</t>
         </is>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="H64" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I64" t="n">
@@ -2929,10 +2926,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B65" s="3" t="n">
+      <c r="A65" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B65" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -2960,7 +2957,7 @@
           <t>GHK_954_1210631378_2602500003324</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I65" t="n">
@@ -2968,10 +2965,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B66" s="3" t="n">
+      <c r="A66" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B66" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -2999,7 +2996,7 @@
           <t>GHK_954_2218689244_2602500004423</t>
         </is>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I66" t="n">
@@ -3007,10 +3004,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B67" s="3" t="n">
+      <c r="A67" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B67" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -3038,7 +3035,7 @@
           <t>GHK_954_1330646892_2602500003321</t>
         </is>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I67" t="n">
@@ -3046,10 +3043,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B68" s="3" t="n">
+      <c r="A68" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B68" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -3077,7 +3074,7 @@
           <t>GHK_954_2474692049_2602500003902</t>
         </is>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I68" t="n">
@@ -3085,10 +3082,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B69" s="3" t="n">
+      <c r="A69" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B69" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -3116,7 +3113,7 @@
           <t>GHK_954_2490919855_2602500004515</t>
         </is>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H69" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I69" t="n">
@@ -3124,10 +3121,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B70" s="3" t="n">
+      <c r="A70" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B70" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,7 +3152,7 @@
           <t>GHK_954_2333987762_2602500003812</t>
         </is>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I70" t="n">
@@ -3163,10 +3160,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B71" s="3" t="n">
+      <c r="A71" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B71" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -3194,7 +3191,7 @@
           <t>GHK_954_0228167664_2602500003748</t>
         </is>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I71" t="n">
@@ -3202,10 +3199,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B72" s="3" t="n">
+      <c r="A72" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B72" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -3233,7 +3230,7 @@
           <t>GHK_954_2490920473_2602500002929</t>
         </is>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I72" t="n">
@@ -3241,10 +3238,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B73" s="3" t="n">
+      <c r="A73" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B73" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -3272,7 +3269,7 @@
           <t>GHK_954_2490924731_2602500004220</t>
         </is>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I73" t="n">
@@ -3280,10 +3277,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B74" s="3" t="n">
+      <c r="A74" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B74" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -3311,7 +3308,7 @@
           <t>GHK_954_2374581680_2602500002827</t>
         </is>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I74" t="n">
@@ -3319,10 +3316,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B75" s="3" t="n">
+      <c r="A75" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B75" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -3350,7 +3347,7 @@
           <t>GHK_954_0132605197_2602500005122</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I75" t="n">
@@ -3358,10 +3355,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B76" s="3" t="n">
+      <c r="A76" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B76" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -3389,7 +3386,7 @@
           <t>GHK_954_0522542679_2602500003011</t>
         </is>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I76" t="n">
@@ -3397,10 +3394,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B77" s="3" t="n">
+      <c r="A77" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B77" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -3428,7 +3425,7 @@
           <t>GHK_954_2490921141_2602500004549</t>
         </is>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I77" t="n">
@@ -3436,10 +3433,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B78" s="3" t="n">
+      <c r="A78" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B78" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -3467,7 +3464,7 @@
           <t>GHK_954_0895286797_2602500003101</t>
         </is>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="H78" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I78" t="n">
@@ -3475,10 +3472,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B79" s="3" t="n">
+      <c r="A79" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B79" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -3506,7 +3503,7 @@
           <t>GHK_954_1089406381_2602500003254</t>
         </is>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I79" t="n">
@@ -3514,10 +3511,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B80" s="3" t="n">
+      <c r="A80" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B80" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -3545,7 +3542,7 @@
           <t>GHK_954_2490921604_2602600005018</t>
         </is>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H80" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I80" t="n">
@@ -3553,10 +3550,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B81" s="3" t="n">
+      <c r="A81" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B81" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -3584,7 +3581,7 @@
           <t>GHK_954_2490921612_2602600002826</t>
         </is>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I81" t="n">
@@ -3592,10 +3589,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B82" s="3" t="n">
+      <c r="A82" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B82" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -3623,7 +3620,7 @@
           <t>GHK_954_2490922057_2602600003032</t>
         </is>
       </c>
-      <c r="H82" s="4" t="n">
+      <c r="H82" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I82" t="n">
@@ -3631,10 +3628,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B83" s="3" t="n">
+      <c r="A83" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B83" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -3662,7 +3659,7 @@
           <t>GHK_954_2490922206_2602600004522</t>
         </is>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I83" t="n">
@@ -3670,10 +3667,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B84" s="3" t="n">
+      <c r="A84" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B84" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -3701,7 +3698,7 @@
           <t>GHK_954_2361695907_2602600004914</t>
         </is>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I84" t="n">
@@ -3709,10 +3706,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B85" s="3" t="n">
+      <c r="A85" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B85" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -3740,7 +3737,7 @@
           <t>GHK_954_2490924806_2602600002958</t>
         </is>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I85" t="n">
@@ -3748,10 +3745,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B86" s="3" t="n">
+      <c r="A86" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B86" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -3779,7 +3776,7 @@
           <t>GHK_954_2066759602_2602600003433</t>
         </is>
       </c>
-      <c r="H86" s="4" t="n">
+      <c r="H86" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I86" t="n">
@@ -3787,10 +3784,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B87" s="3" t="n">
+      <c r="A87" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B87" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -3818,7 +3815,7 @@
           <t>GHK_954_2490925076_2602601002629</t>
         </is>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I87" t="n">
@@ -3826,10 +3823,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B88" s="3" t="n">
+      <c r="A88" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B88" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -3857,7 +3854,7 @@
           <t>GHK_954_0438578098_2602600004459</t>
         </is>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="H88" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I88" t="n">
@@ -3865,10 +3862,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B89" s="3" t="n">
+      <c r="A89" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B89" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -3896,7 +3893,7 @@
           <t>GHK_954_0917775058_2602600005037</t>
         </is>
       </c>
-      <c r="H89" s="4" t="n">
+      <c r="H89" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I89" t="n">
@@ -3904,10 +3901,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B90" s="3" t="n">
+      <c r="A90" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B90" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -3935,7 +3932,7 @@
           <t>GHK_954_2407063557_2602600002833</t>
         </is>
       </c>
-      <c r="H90" s="4" t="n">
+      <c r="H90" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I90" t="n">
@@ -3943,10 +3940,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B91" s="3" t="n">
+      <c r="A91" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B91" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -3974,7 +3971,7 @@
           <t>GHK_954_2404179059_2602600003040</t>
         </is>
       </c>
-      <c r="H91" s="4" t="n">
+      <c r="H91" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I91" t="n">
@@ -3982,10 +3979,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B92" s="3" t="n">
+      <c r="A92" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B92" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -4013,7 +4010,7 @@
           <t>GHK_954_1596457737_2602600005156</t>
         </is>
       </c>
-      <c r="H92" s="4" t="n">
+      <c r="H92" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I92" t="n">
@@ -4021,10 +4018,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B93" s="3" t="n">
+      <c r="A93" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B93" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -4052,7 +4049,7 @@
           <t>GHK_954_1560374918_2602600004104</t>
         </is>
       </c>
-      <c r="H93" s="4" t="n">
+      <c r="H93" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I93" t="n">
@@ -4060,10 +4057,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B94" s="3" t="n">
+      <c r="A94" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B94" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -4091,7 +4088,7 @@
           <t>GHK_954_2490925589_2602600002721</t>
         </is>
       </c>
-      <c r="H94" s="4" t="n">
+      <c r="H94" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I94" t="n">
@@ -4099,10 +4096,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B95" s="3" t="n">
+      <c r="A95" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B95" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -4130,7 +4127,7 @@
           <t>GHK_954_0249510736_2602600003426</t>
         </is>
       </c>
-      <c r="H95" s="4" t="n">
+      <c r="H95" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I95" t="n">
@@ -4138,10 +4135,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B96" s="3" t="n">
+      <c r="A96" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B96" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -4169,7 +4166,7 @@
           <t>GHK_954_2490925738_2602600003340</t>
         </is>
       </c>
-      <c r="H96" s="4" t="n">
+      <c r="H96" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I96" t="n">
@@ -4177,10 +4174,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B97" s="3" t="n">
+      <c r="A97" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B97" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -4208,7 +4205,7 @@
           <t>GHK_954_1316696036_2602600004828</t>
         </is>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I97" t="n">
@@ -4216,10 +4213,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B98" s="3" t="n">
+      <c r="A98" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B98" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -4247,7 +4244,7 @@
           <t>GHK_954_2473856439_2602602002738</t>
         </is>
       </c>
-      <c r="H98" s="4" t="n">
+      <c r="H98" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I98" t="n">
@@ -4255,10 +4252,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B99" s="3" t="n">
+      <c r="A99" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B99" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -4286,7 +4283,7 @@
           <t>GHK_954_2304767706_2602600004001</t>
         </is>
       </c>
-      <c r="H99" s="4" t="n">
+      <c r="H99" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I99" t="n">
@@ -4294,10 +4291,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B100" s="3" t="n">
+      <c r="A100" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B100" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -4325,7 +4322,7 @@
           <t>GHK_954_2490932437_2602600004849</t>
         </is>
       </c>
-      <c r="H100" s="4" t="n">
+      <c r="H100" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I100" t="n">
@@ -4333,10 +4330,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B101" s="3" t="n">
+      <c r="A101" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B101" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -4364,7 +4361,7 @@
           <t>GHK_954_2470145109_2602600003118</t>
         </is>
       </c>
-      <c r="H101" s="4" t="n">
+      <c r="H101" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I101" t="n">
@@ -4372,10 +4369,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B102" s="3" t="n">
+      <c r="A102" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B102" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -4403,7 +4400,7 @@
           <t>GHK_954_2070323148_2602600003701</t>
         </is>
       </c>
-      <c r="H102" s="4" t="n">
+      <c r="H102" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I102" t="n">
@@ -4411,10 +4408,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B103" s="3" t="n">
+      <c r="A103" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B103" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -4442,7 +4439,7 @@
           <t>GHK_954_1530815719_2602600003419</t>
         </is>
       </c>
-      <c r="H103" s="4" t="n">
+      <c r="H103" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I103" t="n">
@@ -4450,10 +4447,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B104" s="3" t="n">
+      <c r="A104" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B104" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -4481,7 +4478,7 @@
           <t>GHK_954_0225595867_2602600002657</t>
         </is>
       </c>
-      <c r="H104" s="4" t="n">
+      <c r="H104" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I104" t="n">
@@ -4489,10 +4486,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B105" s="3" t="n">
+      <c r="A105" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B105" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -4520,7 +4517,7 @@
           <t>GHK_954_2469178939_2602600004409</t>
         </is>
       </c>
-      <c r="H105" s="4" t="n">
+      <c r="H105" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I105" t="n">
@@ -4528,10 +4525,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B106" s="3" t="n">
+      <c r="A106" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B106" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -4559,7 +4556,7 @@
           <t>GHK_954_2490926959_2602600003927</t>
         </is>
       </c>
-      <c r="H106" s="4" t="n">
+      <c r="H106" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I106" t="n">
@@ -4567,10 +4564,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B107" s="3" t="n">
+      <c r="A107" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B107" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -4598,7 +4595,7 @@
           <t>GHK_954_1030021164_2602600003912</t>
         </is>
       </c>
-      <c r="H107" s="4" t="n">
+      <c r="H107" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I107" t="n">
@@ -4606,10 +4603,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B108" s="3" t="n">
+      <c r="A108" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B108" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -4637,7 +4634,7 @@
           <t>GHK_954_2130690056_2602600005207</t>
         </is>
       </c>
-      <c r="H108" s="4" t="n">
+      <c r="H108" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I108" t="n">
@@ -4645,10 +4642,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B109" s="3" t="n">
+      <c r="A109" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B109" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -4676,7 +4673,7 @@
           <t>GHK_954_1469620288_2602600004219</t>
         </is>
       </c>
-      <c r="H109" s="4" t="n">
+      <c r="H109" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I109" t="n">
@@ -4684,10 +4681,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B110" s="3" t="n">
+      <c r="A110" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B110" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -4715,7 +4712,7 @@
           <t>GHK_954_2471373502_2602600003603</t>
         </is>
       </c>
-      <c r="H110" s="4" t="n">
+      <c r="H110" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I110" t="n">
@@ -4723,10 +4720,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B111" s="3" t="n">
+      <c r="A111" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B111" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -4754,7 +4751,7 @@
           <t>GHK_954_0891116006_2602600004122</t>
         </is>
       </c>
-      <c r="H111" s="4" t="n">
+      <c r="H111" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I111" t="n">
@@ -4762,10 +4759,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B112" s="3" t="n">
+      <c r="A112" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B112" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -4793,7 +4790,7 @@
           <t>GHK_954_2490927775_2602600004831</t>
         </is>
       </c>
-      <c r="H112" s="4" t="n">
+      <c r="H112" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I112" t="n">
@@ -4801,10 +4798,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B113" s="3" t="n">
+      <c r="A113" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B113" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -4832,7 +4829,7 @@
           <t>GHK_954_2490927791_2602600005034</t>
         </is>
       </c>
-      <c r="H113" s="4" t="n">
+      <c r="H113" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I113" t="n">
@@ -4840,10 +4837,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B114" s="3" t="n">
+      <c r="A114" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B114" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -4871,7 +4868,7 @@
           <t>GHK_954_2490927957_2602600003334</t>
         </is>
       </c>
-      <c r="H114" s="4" t="n">
+      <c r="H114" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I114" t="n">
@@ -4879,10 +4876,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B115" s="3" t="n">
+      <c r="A115" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B115" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -4910,7 +4907,7 @@
           <t>GHK_954_2490907793_2602600002901</t>
         </is>
       </c>
-      <c r="H115" s="4" t="n">
+      <c r="H115" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I115" t="n">
@@ -4918,10 +4915,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B116" s="3" t="n">
+      <c r="A116" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B116" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -4949,7 +4946,7 @@
           <t>GHK_954_2489349841_2602600003434</t>
         </is>
       </c>
-      <c r="H116" s="4" t="n">
+      <c r="H116" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I116" t="n">
@@ -4957,10 +4954,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B117" s="3" t="n">
+      <c r="A117" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B117" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -4988,7 +4985,7 @@
           <t>GHK_954_2490928229_2602600003021</t>
         </is>
       </c>
-      <c r="H117" s="4" t="n">
+      <c r="H117" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I117" t="n">
@@ -4996,10 +4993,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B118" s="3" t="n">
+      <c r="A118" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B118" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -5027,7 +5024,7 @@
           <t>GHK_954_2490928245_2602600002943</t>
         </is>
       </c>
-      <c r="H118" s="4" t="n">
+      <c r="H118" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I118" t="n">
@@ -5035,10 +5032,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B119" s="3" t="n">
+      <c r="A119" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B119" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -5066,7 +5063,7 @@
           <t>GHK_954_2490928278_2602600003848</t>
         </is>
       </c>
-      <c r="H119" s="4" t="n">
+      <c r="H119" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I119" t="n">
@@ -5074,10 +5071,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B120" s="3" t="n">
+      <c r="A120" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B120" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -5105,7 +5102,7 @@
           <t>GHK_954_2189816602_2602602002612</t>
         </is>
       </c>
-      <c r="H120" s="4" t="n">
+      <c r="H120" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I120" t="n">
@@ -5113,10 +5110,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B121" s="3" t="n">
+      <c r="A121" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B121" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -5144,7 +5141,7 @@
           <t>GHK_954_1053048482_2602600003057</t>
         </is>
       </c>
-      <c r="H121" s="4" t="n">
+      <c r="H121" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I121" t="n">
@@ -5152,10 +5149,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B122" s="3" t="n">
+      <c r="A122" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B122" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -5183,7 +5180,7 @@
           <t>GHK_954_2490928534_2602600003817</t>
         </is>
       </c>
-      <c r="H122" s="4" t="n">
+      <c r="H122" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I122" t="n">
@@ -5191,10 +5188,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B123" s="3" t="n">
+      <c r="A123" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B123" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -5222,7 +5219,7 @@
           <t>GHK_954_0508307949_2602601002614</t>
         </is>
       </c>
-      <c r="H123" s="4" t="n">
+      <c r="H123" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I123" t="n">
@@ -5230,10 +5227,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B124" s="3" t="n">
+      <c r="A124" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B124" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -5261,7 +5258,7 @@
           <t>GHK_954_0223189135_2602600005152</t>
         </is>
       </c>
-      <c r="H124" s="4" t="n">
+      <c r="H124" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I124" t="n">
@@ -5269,10 +5266,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B125" s="3" t="n">
+      <c r="A125" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B125" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -5300,7 +5297,7 @@
           <t>GHK_954_2490928765_2602600003706</t>
         </is>
       </c>
-      <c r="H125" s="4" t="n">
+      <c r="H125" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I125" t="n">
@@ -5308,10 +5305,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B126" s="3" t="n">
+      <c r="A126" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B126" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -5339,7 +5336,7 @@
           <t>GHK_954_2490928815_2602600003329</t>
         </is>
       </c>
-      <c r="H126" s="4" t="n">
+      <c r="H126" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I126" t="n">
@@ -5347,10 +5344,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B127" s="3" t="n">
+      <c r="A127" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B127" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -5378,7 +5375,7 @@
           <t>GHK_954_2490932502_2602600003842</t>
         </is>
       </c>
-      <c r="H127" s="4" t="n">
+      <c r="H127" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I127" t="n">
@@ -5386,10 +5383,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B128" s="3" t="n">
+      <c r="A128" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B128" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -5417,7 +5414,7 @@
           <t>GHK_954_2480718127_2602600003942</t>
         </is>
       </c>
-      <c r="H128" s="4" t="n">
+      <c r="H128" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I128" t="n">
@@ -5425,10 +5422,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B129" s="3" t="n">
+      <c r="A129" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B129" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -5456,7 +5453,7 @@
           <t>GHK_954_2376594921_2602600004131</t>
         </is>
       </c>
-      <c r="H129" s="4" t="n">
+      <c r="H129" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I129" t="n">
@@ -5464,10 +5461,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B130" s="3" t="n">
+      <c r="A130" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B130" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -5495,7 +5492,7 @@
           <t>GHK_954_2490929615_2602600005050</t>
         </is>
       </c>
-      <c r="H130" s="4" t="n">
+      <c r="H130" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I130" t="n">
@@ -5503,10 +5500,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B131" s="3" t="n">
+      <c r="A131" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B131" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -5534,7 +5531,7 @@
           <t>GHK_954_2490932510_2602600003614</t>
         </is>
       </c>
-      <c r="H131" s="4" t="n">
+      <c r="H131" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I131" t="n">
@@ -5542,10 +5539,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B132" s="3" t="n">
+      <c r="A132" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B132" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -5573,7 +5570,7 @@
           <t>GHK_954_2075117560_2602300130742</t>
         </is>
       </c>
-      <c r="H132" s="4" t="n">
+      <c r="H132" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I132" t="n">
@@ -5581,10 +5578,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B133" s="3" t="n">
+      <c r="A133" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B133" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -5612,7 +5609,7 @@
           <t>GHK_954_2282359633_2602400132233</t>
         </is>
       </c>
-      <c r="H133" s="4" t="n">
+      <c r="H133" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I133" t="n">
@@ -5620,10 +5617,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B134" s="3" t="n">
+      <c r="A134" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B134" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -5651,7 +5648,7 @@
           <t>GHK_954_2459917239_2602501093237</t>
         </is>
       </c>
-      <c r="H134" s="4" t="n">
+      <c r="H134" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I134" t="n">
@@ -5659,10 +5656,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B135" s="3" t="n">
+      <c r="A135" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B135" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -5690,7 +5687,7 @@
           <t>GHK_954_2518709528_2602500121502</t>
         </is>
       </c>
-      <c r="H135" s="4" t="n">
+      <c r="H135" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I135" t="n">
@@ -5698,10 +5695,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B136" s="3" t="n">
+      <c r="A136" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B136" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -5729,7 +5726,7 @@
           <t>GHK_954_2471771812_2602600011329</t>
         </is>
       </c>
-      <c r="H136" s="4" t="n">
+      <c r="H136" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I136" t="n">
@@ -5737,10 +5734,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B137" s="3" t="n">
+      <c r="A137" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B137" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C137" t="inlineStr">
@@ -5768,7 +5765,7 @@
           <t>GHK_954_2518697038_2602300114305</t>
         </is>
       </c>
-      <c r="H137" s="4" t="n">
+      <c r="H137" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I137" t="n">
@@ -5776,10 +5773,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B138" s="3" t="n">
+      <c r="A138" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B138" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -5807,7 +5804,7 @@
           <t>GHK_954_2518699455_2602300152246</t>
         </is>
       </c>
-      <c r="H138" s="4" t="n">
+      <c r="H138" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I138" t="n">
@@ -5815,10 +5812,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B139" s="3" t="n">
+      <c r="A139" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B139" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -5846,7 +5843,7 @@
           <t>GHK_954_2518703695_2602300222737</t>
         </is>
       </c>
-      <c r="H139" s="4" t="n">
+      <c r="H139" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I139" t="n">
@@ -5854,10 +5851,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B140" s="3" t="n">
+      <c r="A140" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B140" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C140" t="inlineStr">
@@ -5885,7 +5882,7 @@
           <t>GHK_954_0923041552_2602500133102</t>
         </is>
       </c>
-      <c r="H140" s="4" t="n">
+      <c r="H140" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I140" t="n">
@@ -5893,10 +5890,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B141" s="3" t="n">
+      <c r="A141" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B141" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C141" t="inlineStr">
@@ -5924,7 +5921,7 @@
           <t>GHK_954_2518705617_2602400123302</t>
         </is>
       </c>
-      <c r="H141" s="4" t="n">
+      <c r="H141" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I141" t="n">
@@ -5932,10 +5929,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B142" s="3" t="n">
+      <c r="A142" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B142" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C142" t="inlineStr">
@@ -5963,7 +5960,7 @@
           <t>GHK_954_2518709932_2602500133142</t>
         </is>
       </c>
-      <c r="H142" s="4" t="n">
+      <c r="H142" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I142" t="n">
@@ -5971,10 +5968,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B143" s="3" t="n">
+      <c r="A143" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B143" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C143" t="inlineStr">
@@ -6002,7 +5999,7 @@
           <t>GHK_954_0990356008_2602500082031</t>
         </is>
       </c>
-      <c r="H143" s="4" t="n">
+      <c r="H143" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I143" t="n">
@@ -6010,10 +6007,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B144" s="3" t="n">
+      <c r="A144" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B144" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C144" t="inlineStr">
@@ -6041,7 +6038,7 @@
           <t>GHK_954_2518708884_2602500103744</t>
         </is>
       </c>
-      <c r="H144" s="4" t="n">
+      <c r="H144" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I144" t="n">
@@ -6049,10 +6046,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B145" s="3" t="n">
+      <c r="A145" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B145" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -6080,7 +6077,7 @@
           <t>GHK_954_2518716879_2602500170239</t>
         </is>
       </c>
-      <c r="H145" s="4" t="n">
+      <c r="H145" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I145" t="n">
@@ -6088,10 +6085,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B146" s="3" t="n">
+      <c r="A146" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B146" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -6119,7 +6116,7 @@
           <t>GHK_954_2518697467_2602300130619</t>
         </is>
       </c>
-      <c r="H146" s="4" t="n">
+      <c r="H146" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I146" t="n">
@@ -6127,10 +6124,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B147" s="3" t="n">
+      <c r="A147" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B147" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C147" t="inlineStr">
@@ -6158,7 +6155,7 @@
           <t>GHK_954_2518703299_2602300182249</t>
         </is>
       </c>
-      <c r="H147" s="4" t="n">
+      <c r="H147" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I147" t="n">
@@ -6166,10 +6163,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B148" s="3" t="n">
+      <c r="A148" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B148" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C148" t="inlineStr">
@@ -6197,7 +6194,7 @@
           <t>GHK_954_2263355352_2602300201244</t>
         </is>
       </c>
-      <c r="H148" s="4" t="n">
+      <c r="H148" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I148" t="n">
@@ -6205,10 +6202,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B149" s="3" t="n">
+      <c r="A149" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B149" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -6236,7 +6233,7 @@
           <t>GHK_954_2518703976_2602400070334</t>
         </is>
       </c>
-      <c r="H149" s="4" t="n">
+      <c r="H149" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I149" t="n">
@@ -6244,10 +6241,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B150" s="3" t="n">
+      <c r="A150" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B150" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C150" t="inlineStr">
@@ -6275,7 +6272,7 @@
           <t>GHK_954_0226411544_2602400125741</t>
         </is>
       </c>
-      <c r="H150" s="4" t="n">
+      <c r="H150" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I150" t="n">
@@ -6283,10 +6280,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B151" s="3" t="n">
+      <c r="A151" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B151" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C151" t="inlineStr">
@@ -6314,7 +6311,7 @@
           <t>GHK_954_2518706177_2602400143236</t>
         </is>
       </c>
-      <c r="H151" s="4" t="n">
+      <c r="H151" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I151" t="n">
@@ -6322,10 +6319,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B152" s="3" t="n">
+      <c r="A152" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B152" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C152" t="inlineStr">
@@ -6353,7 +6350,7 @@
           <t>GHK_954_2518709742_2602500130750</t>
         </is>
       </c>
-      <c r="H152" s="4" t="n">
+      <c r="H152" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I152" t="n">
@@ -6361,10 +6358,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B153" s="3" t="n">
+      <c r="A153" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B153" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C153" t="inlineStr">
@@ -6392,7 +6389,7 @@
           <t>GHK_954_2389980802_2602500200745</t>
         </is>
       </c>
-      <c r="H153" s="4" t="n">
+      <c r="H153" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I153" t="n">
@@ -6400,10 +6397,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B154" s="3" t="n">
+      <c r="A154" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B154" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C154" t="inlineStr">
@@ -6431,7 +6428,7 @@
           <t>GHK_954_2518698937_2602300144733</t>
         </is>
       </c>
-      <c r="H154" s="4" t="n">
+      <c r="H154" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I154" t="n">
@@ -6439,10 +6436,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B155" s="3" t="n">
+      <c r="A155" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B155" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C155" t="inlineStr">
@@ -6470,7 +6467,7 @@
           <t>GHK_954_0232157404_2602401131256</t>
         </is>
       </c>
-      <c r="H155" s="4" t="n">
+      <c r="H155" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I155" t="n">
@@ -6478,10 +6475,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B156" s="3" t="n">
+      <c r="A156" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B156" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -6509,7 +6506,7 @@
           <t>GHK_954_1294813751_2602400131302</t>
         </is>
       </c>
-      <c r="H156" s="4" t="n">
+      <c r="H156" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I156" t="n">
@@ -6517,10 +6514,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B157" s="3" t="n">
+      <c r="A157" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B157" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C157" t="inlineStr">
@@ -6548,7 +6545,7 @@
           <t>GHK_954_2518706078_2602400141345</t>
         </is>
       </c>
-      <c r="H157" s="4" t="n">
+      <c r="H157" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I157" t="n">
@@ -6556,10 +6553,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B158" s="3" t="n">
+      <c r="A158" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B158" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C158" t="inlineStr">
@@ -6587,7 +6584,7 @@
           <t>GHK_954_1594092023_2602500133125</t>
         </is>
       </c>
-      <c r="H158" s="4" t="n">
+      <c r="H158" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I158" t="n">
@@ -6595,10 +6592,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B159" s="3" t="n">
+      <c r="A159" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B159" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C159" t="inlineStr">
@@ -6626,7 +6623,7 @@
           <t>GHK_954_2518706334_2602400151239</t>
         </is>
       </c>
-      <c r="H159" s="4" t="n">
+      <c r="H159" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I159" t="n">
@@ -6634,10 +6631,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B160" s="3" t="n">
+      <c r="A160" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B160" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C160" t="inlineStr">
@@ -6665,7 +6662,7 @@
           <t>GHK_954_2472424239_2602500140737</t>
         </is>
       </c>
-      <c r="H160" s="4" t="n">
+      <c r="H160" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I160" t="n">
@@ -6673,10 +6670,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B161" s="3" t="n">
+      <c r="A161" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B161" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C161" t="inlineStr">
@@ -6704,7 +6701,7 @@
           <t>GHK_954_2179710385_2602601111805</t>
         </is>
       </c>
-      <c r="H161" s="4" t="n">
+      <c r="H161" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I161" t="n">
@@ -6712,10 +6709,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B162" s="3" t="n">
+      <c r="A162" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B162" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C162" t="inlineStr">
@@ -6743,7 +6740,7 @@
           <t>GHK_954_2518730904_2602600131811</t>
         </is>
       </c>
-      <c r="H162" s="4" t="n">
+      <c r="H162" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I162" t="n">
@@ -6751,10 +6748,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B163" s="3" t="n">
+      <c r="A163" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B163" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C163" t="inlineStr">
@@ -6782,7 +6779,7 @@
           <t>GHK_954_2518697293_2602300123751</t>
         </is>
       </c>
-      <c r="H163" s="4" t="n">
+      <c r="H163" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I163" t="n">
@@ -6790,10 +6787,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B164" s="3" t="n">
+      <c r="A164" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B164" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C164" t="inlineStr">
@@ -6821,7 +6818,7 @@
           <t>GHK_954_2389728730_2602300182738</t>
         </is>
       </c>
-      <c r="H164" s="4" t="n">
+      <c r="H164" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I164" t="n">
@@ -6829,10 +6826,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B165" s="3" t="n">
+      <c r="A165" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B165" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C165" t="inlineStr">
@@ -6860,7 +6857,7 @@
           <t>GHK_954_2518709304_2602500113242</t>
         </is>
       </c>
-      <c r="H165" s="4" t="n">
+      <c r="H165" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I165" t="n">
@@ -6868,10 +6865,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B166" s="3" t="n">
+      <c r="A166" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B166" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C166" t="inlineStr">
@@ -6899,7 +6896,7 @@
           <t>GHK_954_1574973929_2602502133241</t>
         </is>
       </c>
-      <c r="H166" s="4" t="n">
+      <c r="H166" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I166" t="n">
@@ -6907,10 +6904,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B167" s="3" t="n">
+      <c r="A167" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B167" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C167" t="inlineStr">
@@ -6938,7 +6935,7 @@
           <t>GHK_954_2517341232_2602500125757</t>
         </is>
       </c>
-      <c r="H167" s="4" t="n">
+      <c r="H167" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I167" t="n">
@@ -6946,10 +6943,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B168" s="3" t="n">
+      <c r="A168" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B168" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C168" t="inlineStr">
@@ -6977,7 +6974,7 @@
           <t>GHK_954_2518717778_2602600070347</t>
         </is>
       </c>
-      <c r="H168" s="4" t="n">
+      <c r="H168" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I168" t="n">
@@ -6985,10 +6982,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B169" s="3" t="n">
+      <c r="A169" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B169" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C169" t="inlineStr">
@@ -7016,7 +7013,7 @@
           <t>GHK_954_1119458501_2602601094238</t>
         </is>
       </c>
-      <c r="H169" s="4" t="n">
+      <c r="H169" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I169" t="n">
@@ -7024,10 +7021,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B170" s="3" t="n">
+      <c r="A170" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B170" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C170" t="inlineStr">
@@ -7055,7 +7052,7 @@
           <t>GHK_954_2518720459_2602600102737</t>
         </is>
       </c>
-      <c r="H170" s="4" t="n">
+      <c r="H170" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I170" t="n">
@@ -7063,10 +7060,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B171" s="3" t="n">
+      <c r="A171" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B171" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C171" t="inlineStr">
@@ -7094,7 +7091,7 @@
           <t>GHK_954_2523931778_2602600160836</t>
         </is>
       </c>
-      <c r="H171" s="4" t="n">
+      <c r="H171" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I171" t="n">
@@ -7102,10 +7099,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B172" s="3" t="n">
+      <c r="A172" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B172" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C172" t="inlineStr">
@@ -7133,7 +7130,7 @@
           <t>GHK_954_2482233000_2602600113751</t>
         </is>
       </c>
-      <c r="H172" s="4" t="n">
+      <c r="H172" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I172" t="n">
@@ -7141,10 +7138,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B173" s="3" t="n">
+      <c r="A173" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B173" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C173" t="inlineStr">
@@ -7172,7 +7169,7 @@
           <t>GHK_954_2190047551_2602601124259</t>
         </is>
       </c>
-      <c r="H173" s="4" t="n">
+      <c r="H173" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I173" t="n">
@@ -7180,10 +7177,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B174" s="3" t="n">
+      <c r="A174" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B174" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C174" t="inlineStr">
@@ -7211,7 +7208,7 @@
           <t>GHK_954_2523936306_2602600173849</t>
         </is>
       </c>
-      <c r="H174" s="4" t="n">
+      <c r="H174" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I174" t="n">
@@ -7219,10 +7216,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B175" s="3" t="n">
+      <c r="A175" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B175" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C175" t="inlineStr">
@@ -7250,7 +7247,7 @@
           <t>GHK_954_0510371586_2602500072821</t>
         </is>
       </c>
-      <c r="H175" s="4" t="n">
+      <c r="H175" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I175" t="n">
@@ -7258,10 +7255,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B176" s="3" t="n">
+      <c r="A176" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B176" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C176" t="inlineStr">
@@ -7289,7 +7286,7 @@
           <t>GHK_954_2518708298_2602500084306</t>
         </is>
       </c>
-      <c r="H176" s="4" t="n">
+      <c r="H176" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I176" t="n">
@@ -7297,10 +7294,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B177" s="3" t="n">
+      <c r="A177" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B177" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C177" t="inlineStr">
@@ -7328,7 +7325,7 @@
           <t>GHK_954_0265070789_2602500101257</t>
         </is>
       </c>
-      <c r="H177" s="4" t="n">
+      <c r="H177" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I177" t="n">
@@ -7336,10 +7333,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B178" s="3" t="n">
+      <c r="A178" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B178" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C178" t="inlineStr">
@@ -7367,7 +7364,7 @@
           <t>GHK_954_2426076192_2602500111740</t>
         </is>
       </c>
-      <c r="H178" s="4" t="n">
+      <c r="H178" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I178" t="n">
@@ -7375,10 +7372,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B179" s="3" t="n">
+      <c r="A179" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B179" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C179" t="inlineStr">
@@ -7406,7 +7403,7 @@
           <t>GHK_954_2490927767_2602610120449</t>
         </is>
       </c>
-      <c r="H179" s="4" t="n">
+      <c r="H179" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I179" t="n">
@@ -7414,10 +7411,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B180" s="3" t="n">
+      <c r="A180" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B180" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -7445,7 +7442,7 @@
           <t>GHK_954_2057298560_2602600171750</t>
         </is>
       </c>
-      <c r="H180" s="4" t="n">
+      <c r="H180" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I180" t="n">
@@ -7453,10 +7450,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B181" s="3" t="n">
+      <c r="A181" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B181" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C181" t="inlineStr">
@@ -7484,7 +7481,7 @@
           <t>GHK_954_1609037476_2602300130923</t>
         </is>
       </c>
-      <c r="H181" s="4" t="n">
+      <c r="H181" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I181" t="n">
@@ -7492,10 +7489,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B182" s="3" t="n">
+      <c r="A182" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B182" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C182" t="inlineStr">
@@ -7523,7 +7520,7 @@
           <t>GHK_954_2518704982_2602405103259</t>
         </is>
       </c>
-      <c r="H182" s="4" t="n">
+      <c r="H182" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I182" t="n">
@@ -7531,10 +7528,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B183" s="3" t="n">
+      <c r="A183" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B183" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C183" t="inlineStr">
@@ -7562,7 +7559,7 @@
           <t>GHK_954_2518705922_2602400134736</t>
         </is>
       </c>
-      <c r="H183" s="4" t="n">
+      <c r="H183" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I183" t="n">
@@ -7570,10 +7567,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B184" s="3" t="n">
+      <c r="A184" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B184" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C184" t="inlineStr">
@@ -7601,7 +7598,7 @@
           <t>GHK_954_2518708306_2602500084757</t>
         </is>
       </c>
-      <c r="H184" s="4" t="n">
+      <c r="H184" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I184" t="n">
@@ -7609,10 +7606,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B185" s="3" t="n">
+      <c r="A185" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B185" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C185" t="inlineStr">
@@ -7640,7 +7637,7 @@
           <t>GHK_954_0221816721_2602500113756</t>
         </is>
       </c>
-      <c r="H185" s="4" t="n">
+      <c r="H185" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I185" t="n">
@@ -7648,10 +7645,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B186" s="3" t="n">
+      <c r="A186" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B186" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C186" t="inlineStr">
@@ -7679,7 +7676,7 @@
           <t>GHK_954_2250447022_2602500203737</t>
         </is>
       </c>
-      <c r="H186" s="4" t="n">
+      <c r="H186" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I186" t="n">
@@ -7687,10 +7684,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B187" s="3" t="n">
+      <c r="A187" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B187" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C187" t="inlineStr">
@@ -7718,7 +7715,7 @@
           <t>GHK_954_2451838292_2602600155245</t>
         </is>
       </c>
-      <c r="H187" s="4" t="n">
+      <c r="H187" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I187" t="n">
@@ -7726,10 +7723,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B188" s="3" t="n">
+      <c r="A188" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B188" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C188" t="inlineStr">
@@ -7757,7 +7754,7 @@
           <t>GHK_954_2518703364_2602300190743</t>
         </is>
       </c>
-      <c r="H188" s="4" t="n">
+      <c r="H188" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I188" t="n">
@@ -7765,10 +7762,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B189" s="3" t="n">
+      <c r="A189" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B189" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -7796,7 +7793,7 @@
           <t>GHK_954_0266451301_2602300212242</t>
         </is>
       </c>
-      <c r="H189" s="4" t="n">
+      <c r="H189" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I189" t="n">
@@ -7804,10 +7801,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B190" s="3" t="n">
+      <c r="A190" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B190" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C190" t="inlineStr">
@@ -7835,7 +7832,7 @@
           <t>GHK_954_1436780512_2602400084755</t>
         </is>
       </c>
-      <c r="H190" s="4" t="n">
+      <c r="H190" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I190" t="n">
@@ -7843,10 +7840,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B191" s="3" t="n">
+      <c r="A191" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B191" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C191" t="inlineStr">
@@ -7874,7 +7871,7 @@
           <t>GHK_954_2518705914_2602400134231</t>
         </is>
       </c>
-      <c r="H191" s="4" t="n">
+      <c r="H191" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I191" t="n">
@@ -7882,10 +7879,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B192" s="3" t="n">
+      <c r="A192" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B192" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C192" t="inlineStr">
@@ -7913,7 +7910,7 @@
           <t>GHK_954_2518706219_2602400143737</t>
         </is>
       </c>
-      <c r="H192" s="4" t="n">
+      <c r="H192" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I192" t="n">
@@ -7921,10 +7918,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B193" s="3" t="n">
+      <c r="A193" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B193" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C193" t="inlineStr">
@@ -7952,7 +7949,7 @@
           <t>GHK_954_1102093026_2602500133152</t>
         </is>
       </c>
-      <c r="H193" s="4" t="n">
+      <c r="H193" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I193" t="n">
@@ -7960,10 +7957,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B194" s="3" t="n">
+      <c r="A194" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B194" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C194" t="inlineStr">
@@ -7991,7 +7988,7 @@
           <t>GHK_954_2518708363_2602500085745</t>
         </is>
       </c>
-      <c r="H194" s="4" t="n">
+      <c r="H194" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I194" t="n">
@@ -7999,10 +7996,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B195" s="3" t="n">
+      <c r="A195" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B195" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C195" t="inlineStr">
@@ -8030,7 +8027,7 @@
           <t>GHK_954_2490858426_2602600020251</t>
         </is>
       </c>
-      <c r="H195" s="4" t="n">
+      <c r="H195" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I195" t="n">
@@ -8038,10 +8035,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B196" s="3" t="n">
+      <c r="A196" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B196" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C196" t="inlineStr">
@@ -8069,7 +8066,7 @@
           <t>GHK_954_1289672519_2602600111252</t>
         </is>
       </c>
-      <c r="H196" s="4" t="n">
+      <c r="H196" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I196" t="n">
@@ -8077,10 +8074,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B197" s="3" t="n">
+      <c r="A197" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B197" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C197" t="inlineStr">
@@ -8108,7 +8105,7 @@
           <t>GHK_954_2518706748_2602400170246</t>
         </is>
       </c>
-      <c r="H197" s="4" t="n">
+      <c r="H197" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I197" t="n">
@@ -8116,10 +8113,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B198" s="3" t="n">
+      <c r="A198" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B198" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C198" t="inlineStr">
@@ -8147,7 +8144,7 @@
           <t>GHK_954_2518706896_2602400181109</t>
         </is>
       </c>
-      <c r="H198" s="4" t="n">
+      <c r="H198" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I198" t="n">
@@ -8155,10 +8152,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B199" s="3" t="n">
+      <c r="A199" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B199" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C199" t="inlineStr">
@@ -8186,7 +8183,7 @@
           <t>GHK_954_1001118510_2602400184834</t>
         </is>
       </c>
-      <c r="H199" s="4" t="n">
+      <c r="H199" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I199" t="n">
@@ -8194,10 +8191,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B200" s="3" t="n">
+      <c r="A200" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B200" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C200" t="inlineStr">
@@ -8225,7 +8222,7 @@
           <t>GHK_954_2518709726_2602500130748</t>
         </is>
       </c>
-      <c r="H200" s="4" t="n">
+      <c r="H200" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I200" t="n">
@@ -8233,10 +8230,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B201" s="3" t="n">
+      <c r="A201" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B201" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C201" t="inlineStr">
@@ -8264,7 +8261,7 @@
           <t>GHK_954_2079149114_2602600064751</t>
         </is>
       </c>
-      <c r="H201" s="4" t="n">
+      <c r="H201" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I201" t="n">
@@ -8272,10 +8269,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B202" s="3" t="n">
+      <c r="A202" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B202" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C202" t="inlineStr">
@@ -8303,7 +8300,7 @@
           <t>GHK_954_1258694577_2602600095245</t>
         </is>
       </c>
-      <c r="H202" s="4" t="n">
+      <c r="H202" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I202" t="n">
@@ -8311,10 +8308,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B203" s="3" t="n">
+      <c r="A203" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B203" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C203" t="inlineStr">
@@ -8342,7 +8339,7 @@
           <t>GHK_954_2492789330_2602400090255</t>
         </is>
       </c>
-      <c r="H203" s="4" t="n">
+      <c r="H203" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I203" t="n">
@@ -8350,10 +8347,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B204" s="3" t="n">
+      <c r="A204" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B204" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C204" t="inlineStr">
@@ -8381,7 +8378,7 @@
           <t>GHK_954_1581823232_2602400135245</t>
         </is>
       </c>
-      <c r="H204" s="4" t="n">
+      <c r="H204" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I204" t="n">
@@ -8389,10 +8386,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B205" s="3" t="n">
+      <c r="A205" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B205" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C205" t="inlineStr">
@@ -8420,7 +8417,7 @@
           <t>GHK_954_2452252899_2602500094315</t>
         </is>
       </c>
-      <c r="H205" s="4" t="n">
+      <c r="H205" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I205" t="n">
@@ -8428,10 +8425,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B206" s="3" t="n">
+      <c r="A206" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B206" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C206" t="inlineStr">
@@ -8459,7 +8456,7 @@
           <t>GHK_954_2464450333_2602500160734</t>
         </is>
       </c>
-      <c r="H206" s="4" t="n">
+      <c r="H206" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I206" t="n">
@@ -8467,10 +8464,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B207" s="3" t="n">
+      <c r="A207" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B207" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C207" t="inlineStr">
@@ -8498,7 +8495,7 @@
           <t>GHK_954_0271864837_2602600111813</t>
         </is>
       </c>
-      <c r="H207" s="4" t="n">
+      <c r="H207" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I207" t="n">
@@ -8506,10 +8503,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B208" s="3" t="n">
+      <c r="A208" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B208" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C208" t="inlineStr">
@@ -8537,7 +8534,7 @@
           <t>GHK_954_2523931125_2602600135853</t>
         </is>
       </c>
-      <c r="H208" s="4" t="n">
+      <c r="H208" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I208" t="n">
@@ -8545,10 +8542,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B209" s="3" t="n">
+      <c r="A209" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B209" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C209" t="inlineStr">
@@ -8576,7 +8573,7 @@
           <t>GHK_954_2523936314_2602600173850</t>
         </is>
       </c>
-      <c r="H209" s="4" t="n">
+      <c r="H209" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I209" t="n">
@@ -8584,10 +8581,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B210" s="3" t="n">
+      <c r="A210" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B210" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C210" t="inlineStr">
@@ -8615,7 +8612,7 @@
           <t>GHK_954_2130625029_2602300130651</t>
         </is>
       </c>
-      <c r="H210" s="4" t="n">
+      <c r="H210" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I210" t="n">
@@ -8623,10 +8620,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B211" s="3" t="n">
+      <c r="A211" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B211" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C211" t="inlineStr">
@@ -8654,7 +8651,7 @@
           <t>GHK_954_0879978534_2602400144736</t>
         </is>
       </c>
-      <c r="H211" s="4" t="n">
+      <c r="H211" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I211" t="n">
@@ -8662,10 +8659,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B212" s="3" t="n">
+      <c r="A212" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B212" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C212" t="inlineStr">
@@ -8693,7 +8690,7 @@
           <t>GHK_954_2518709924_2602500133133</t>
         </is>
       </c>
-      <c r="H212" s="4" t="n">
+      <c r="H212" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I212" t="n">
@@ -8701,10 +8698,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B213" s="3" t="n">
+      <c r="A213" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B213" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C213" t="inlineStr">
@@ -8732,7 +8729,7 @@
           <t>GHK_954_2518707126_2602400202735</t>
         </is>
       </c>
-      <c r="H213" s="4" t="n">
+      <c r="H213" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I213" t="n">
@@ -8740,10 +8737,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B214" s="3" t="n">
+      <c r="A214" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B214" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C214" t="inlineStr">
@@ -8771,7 +8768,7 @@
           <t>GHK_954_1435900632_2602600085745</t>
         </is>
       </c>
-      <c r="H214" s="4" t="n">
+      <c r="H214" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I214" t="n">
@@ -8779,10 +8776,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B215" s="3" t="n">
+      <c r="A215" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B215" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C215" t="inlineStr">
@@ -8810,7 +8807,7 @@
           <t>GHK_954_2412211142_2602600094242</t>
         </is>
       </c>
-      <c r="H215" s="4" t="n">
+      <c r="H215" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I215" t="n">
@@ -8818,10 +8815,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B216" s="3" t="n">
+      <c r="A216" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B216" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C216" t="inlineStr">
@@ -8849,7 +8846,7 @@
           <t>GHK_954_0089706022_2602600122447</t>
         </is>
       </c>
-      <c r="H216" s="4" t="n">
+      <c r="H216" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I216" t="n">
@@ -8857,10 +8854,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B217" s="3" t="n">
+      <c r="A217" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B217" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C217" t="inlineStr">
@@ -8888,7 +8885,7 @@
           <t>GHK_954_0162865125_2602400113739</t>
         </is>
       </c>
-      <c r="H217" s="4" t="n">
+      <c r="H217" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I217" t="n">
@@ -8896,10 +8893,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B218" s="3" t="n">
+      <c r="A218" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B218" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C218" t="inlineStr">
@@ -8927,7 +8924,7 @@
           <t>GHK_954_1396496554_2602400114740</t>
         </is>
       </c>
-      <c r="H218" s="4" t="n">
+      <c r="H218" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I218" t="n">
@@ -8935,10 +8932,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B219" s="3" t="n">
+      <c r="A219" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B219" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C219" t="inlineStr">
@@ -8966,7 +8963,7 @@
           <t>GHK_954_2518707761_2602500071738</t>
         </is>
       </c>
-      <c r="H219" s="4" t="n">
+      <c r="H219" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I219" t="n">
@@ -8974,10 +8971,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B220" s="3" t="n">
+      <c r="A220" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B220" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C220" t="inlineStr">
@@ -9005,7 +9002,7 @@
           <t>GHK_954_1227853650_2602500133231</t>
         </is>
       </c>
-      <c r="H220" s="4" t="n">
+      <c r="H220" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I220" t="n">
@@ -9013,10 +9010,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B221" s="3" t="n">
+      <c r="A221" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B221" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C221" t="inlineStr">
@@ -9044,7 +9041,7 @@
           <t>GHK_954_1097092629_2602500133232</t>
         </is>
       </c>
-      <c r="H221" s="4" t="n">
+      <c r="H221" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I221" t="n">
@@ -9052,10 +9049,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B222" s="3" t="n">
+      <c r="A222" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B222" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C222" t="inlineStr">
@@ -9083,7 +9080,7 @@
           <t>GHK_954_2518709403_2602500115246</t>
         </is>
       </c>
-      <c r="H222" s="4" t="n">
+      <c r="H222" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I222" t="n">
@@ -9091,10 +9088,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B223" s="3" t="n">
+      <c r="A223" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B223" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C223" t="inlineStr">
@@ -9122,7 +9119,7 @@
           <t>GHK_954_2518713504_2602500142241</t>
         </is>
       </c>
-      <c r="H223" s="4" t="n">
+      <c r="H223" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I223" t="n">
@@ -9130,10 +9127,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B224" s="3" t="n">
+      <c r="A224" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B224" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C224" t="inlineStr">
@@ -9161,7 +9158,7 @@
           <t>GHK_954_2490919863_2602500153246</t>
         </is>
       </c>
-      <c r="H224" s="4" t="n">
+      <c r="H224" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I224" t="n">
@@ -9169,10 +9166,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B225" s="3" t="n">
+      <c r="A225" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B225" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C225" t="inlineStr">
@@ -9200,7 +9197,7 @@
           <t>GHK_954_2389695442_2602500220321</t>
         </is>
       </c>
-      <c r="H225" s="4" t="n">
+      <c r="H225" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I225" t="n">
@@ -9208,10 +9205,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B226" s="3" t="n">
+      <c r="A226" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B226" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C226" t="inlineStr">
@@ -9239,7 +9236,7 @@
           <t>GHK_954_1102031661_2602600103252</t>
         </is>
       </c>
-      <c r="H226" s="4" t="n">
+      <c r="H226" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I226" t="n">
@@ -9247,10 +9244,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B227" s="3" t="n">
+      <c r="A227" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B227" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C227" t="inlineStr">
@@ -9278,7 +9275,7 @@
           <t>GHK_954_1116475136_2602600160837</t>
         </is>
       </c>
-      <c r="H227" s="4" t="n">
+      <c r="H227" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I227" t="n">
@@ -9286,10 +9283,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B228" s="3" t="n">
+      <c r="A228" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B228" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C228" t="inlineStr">
@@ -9317,7 +9314,7 @@
           <t>GHK_954_1305735985_2602300144220</t>
         </is>
       </c>
-      <c r="H228" s="4" t="n">
+      <c r="H228" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I228" t="n">
@@ -9325,10 +9322,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B229" s="3" t="n">
+      <c r="A229" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B229" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C229" t="inlineStr">
@@ -9356,7 +9353,7 @@
           <t>GHK_954_2518709940_2602500133150</t>
         </is>
       </c>
-      <c r="H229" s="4" t="n">
+      <c r="H229" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I229" t="n">
@@ -9364,10 +9361,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B230" s="3" t="n">
+      <c r="A230" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B230" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C230" t="inlineStr">
@@ -9395,7 +9392,7 @@
           <t>GHK_954_1128982582_2602500133223</t>
         </is>
       </c>
-      <c r="H230" s="4" t="n">
+      <c r="H230" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I230" t="n">
@@ -9403,10 +9400,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B231" s="3" t="n">
+      <c r="A231" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B231" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C231" t="inlineStr">
@@ -9434,7 +9431,7 @@
           <t>GHK_954_0521566943_2602600090256</t>
         </is>
       </c>
-      <c r="H231" s="4" t="n">
+      <c r="H231" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I231" t="n">
@@ -9442,10 +9439,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B232" s="3" t="n">
+      <c r="A232" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B232" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C232" t="inlineStr">
@@ -9473,7 +9470,7 @@
           <t>GHK_954_1114312109_2602602101739</t>
         </is>
       </c>
-      <c r="H232" s="4" t="n">
+      <c r="H232" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I232" t="n">
@@ -9481,10 +9478,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B233" s="3" t="n">
+      <c r="A233" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B233" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C233" t="inlineStr">
@@ -9512,7 +9509,7 @@
           <t>GHK_954_1406975530_2602600144758</t>
         </is>
       </c>
-      <c r="H233" s="4" t="n">
+      <c r="H233" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I233" t="n">
@@ -9520,10 +9517,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B234" s="3" t="n">
+      <c r="A234" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B234" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C234" t="inlineStr">
@@ -9551,7 +9548,7 @@
           <t>GHK_954_0952093078_2602300173736</t>
         </is>
       </c>
-      <c r="H234" s="4" t="n">
+      <c r="H234" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I234" t="n">
@@ -9559,10 +9556,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B235" s="3" t="n">
+      <c r="A235" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B235" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C235" t="inlineStr">
@@ -9590,7 +9587,7 @@
           <t>GHK_954_1237203862_2602500133117</t>
         </is>
       </c>
-      <c r="H235" s="4" t="n">
+      <c r="H235" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I235" t="n">
@@ -9598,10 +9595,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B236" s="3" t="n">
+      <c r="A236" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B236" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C236" t="inlineStr">
@@ -9629,7 +9626,7 @@
           <t>GHK_954_2518706326_2602400151238</t>
         </is>
       </c>
-      <c r="H236" s="4" t="n">
+      <c r="H236" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I236" t="n">
@@ -9637,10 +9634,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B237" s="3" t="n">
+      <c r="A237" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B237" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C237" t="inlineStr">
@@ -9668,7 +9665,7 @@
           <t>GHK_954_0607170875_2602500095737</t>
         </is>
       </c>
-      <c r="H237" s="4" t="n">
+      <c r="H237" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I237" t="n">
@@ -9676,10 +9673,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B238" s="3" t="n">
+      <c r="A238" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B238" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C238" t="inlineStr">
@@ -9707,7 +9704,7 @@
           <t>GHK_954_2518716580_2602501152239</t>
         </is>
       </c>
-      <c r="H238" s="4" t="n">
+      <c r="H238" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I238" t="n">
@@ -9715,10 +9712,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B239" s="3" t="n">
+      <c r="A239" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B239" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C239" t="inlineStr">
@@ -9746,7 +9743,7 @@
           <t>GHK_954_2319668378_2602600100259</t>
         </is>
       </c>
-      <c r="H239" s="4" t="n">
+      <c r="H239" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I239" t="n">
@@ -9754,10 +9751,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B240" s="3" t="n">
+      <c r="A240" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B240" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C240" t="inlineStr">
@@ -9785,7 +9782,7 @@
           <t>GHK_954_1123778423_2602500133154</t>
         </is>
       </c>
-      <c r="H240" s="4" t="n">
+      <c r="H240" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I240" t="n">
@@ -9793,10 +9790,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B241" s="3" t="n">
+      <c r="A241" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B241" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C241" t="inlineStr">
@@ -9824,7 +9821,7 @@
           <t>GHK_954_1369490402_2602500192244</t>
         </is>
       </c>
-      <c r="H241" s="4" t="n">
+      <c r="H241" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I241" t="n">
@@ -9832,10 +9829,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B242" s="3" t="n">
+      <c r="A242" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B242" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C242" t="inlineStr">
@@ -9863,7 +9860,7 @@
           <t>GHK_954_0243086584_2602600155246</t>
         </is>
       </c>
-      <c r="H242" s="4" t="n">
+      <c r="H242" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I242" t="n">
@@ -9871,10 +9868,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B243" s="3" t="n">
+      <c r="A243" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B243" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C243" t="inlineStr">
@@ -9902,7 +9899,7 @@
           <t>GHK_954_2472991344_2602300173738</t>
         </is>
       </c>
-      <c r="H243" s="4" t="n">
+      <c r="H243" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I243" t="n">
@@ -9910,10 +9907,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B244" s="3" t="n">
+      <c r="A244" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B244" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C244" t="inlineStr">
@@ -9941,7 +9938,7 @@
           <t>GHK_954_2167868310_2602400012411</t>
         </is>
       </c>
-      <c r="H244" s="4" t="n">
+      <c r="H244" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I244" t="n">
@@ -9949,10 +9946,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B245" s="3" t="n">
+      <c r="A245" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B245" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C245" t="inlineStr">
@@ -9980,7 +9977,7 @@
           <t>GHK_954_1036128484_2602500081543</t>
         </is>
       </c>
-      <c r="H245" s="4" t="n">
+      <c r="H245" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I245" t="n">
@@ -9988,10 +9985,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B246" s="3" t="n">
+      <c r="A246" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B246" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C246" t="inlineStr">
@@ -10019,7 +10016,7 @@
           <t>GHK_954_2518708272_2602500084302</t>
         </is>
       </c>
-      <c r="H246" s="4" t="n">
+      <c r="H246" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I246" t="n">
@@ -10027,10 +10024,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B247" s="3" t="n">
+      <c r="A247" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B247" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C247" t="inlineStr">
@@ -10058,7 +10055,7 @@
           <t>GHK_954_1353465568_2602500100755</t>
         </is>
       </c>
-      <c r="H247" s="4" t="n">
+      <c r="H247" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I247" t="n">
@@ -10066,10 +10063,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B248" s="3" t="n">
+      <c r="A248" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B248" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C248" t="inlineStr">
@@ -10097,7 +10094,7 @@
           <t>GHK_954_2509583171_2602500151240</t>
         </is>
       </c>
-      <c r="H248" s="4" t="n">
+      <c r="H248" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I248" t="n">
@@ -10105,10 +10102,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B249" s="3" t="n">
+      <c r="A249" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B249" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C249" t="inlineStr">
@@ -10136,7 +10133,7 @@
           <t>GHK_954_0915908693_2602600111804</t>
         </is>
       </c>
-      <c r="H249" s="4" t="n">
+      <c r="H249" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I249" t="n">
@@ -10144,10 +10141,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B250" s="3" t="n">
+      <c r="A250" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B250" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C250" t="inlineStr">
@@ -10175,7 +10172,7 @@
           <t>GHK_954_1324802428_2602500204742</t>
         </is>
       </c>
-      <c r="H250" s="4" t="n">
+      <c r="H250" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I250" t="n">
@@ -10183,10 +10180,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B251" s="3" t="n">
+      <c r="A251" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B251" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C251" t="inlineStr">
@@ -10214,7 +10211,7 @@
           <t>GHK_954_2518723206_2602601111828</t>
         </is>
       </c>
-      <c r="H251" s="4" t="n">
+      <c r="H251" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I251" t="n">
@@ -10222,10 +10219,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B252" s="3" t="n">
+      <c r="A252" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B252" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C252" t="inlineStr">
@@ -10253,7 +10250,7 @@
           <t>GHK_954_2518704495_2602400091300</t>
         </is>
       </c>
-      <c r="H252" s="4" t="n">
+      <c r="H252" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I252" t="n">
@@ -10261,10 +10258,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B253" s="3" t="n">
+      <c r="A253" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B253" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C253" t="inlineStr">
@@ -10292,7 +10289,7 @@
           <t>GHK_954_2518705252_2602400111252</t>
         </is>
       </c>
-      <c r="H253" s="4" t="n">
+      <c r="H253" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I253" t="n">
@@ -10300,10 +10297,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B254" s="3" t="n">
+      <c r="A254" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B254" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C254" t="inlineStr">
@@ -10331,7 +10328,7 @@
           <t>GHK_954_1131290262_2602400164738</t>
         </is>
       </c>
-      <c r="H254" s="4" t="n">
+      <c r="H254" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I254" t="n">
@@ -10339,10 +10336,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B255" s="3" t="n">
+      <c r="A255" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B255" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C255" t="inlineStr">
@@ -10370,7 +10367,7 @@
           <t>GHK_954_0444900773_2602500090309</t>
         </is>
       </c>
-      <c r="H255" s="4" t="n">
+      <c r="H255" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I255" t="n">
@@ -10378,10 +10375,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B256" s="3" t="n">
+      <c r="A256" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B256" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C256" t="inlineStr">
@@ -10409,7 +10406,7 @@
           <t>GHK_954_2518717737_2602600063758</t>
         </is>
       </c>
-      <c r="H256" s="4" t="n">
+      <c r="H256" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I256" t="n">
@@ -10417,10 +10414,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B257" s="3" t="n">
+      <c r="A257" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B257" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C257" t="inlineStr">
@@ -10448,7 +10445,7 @@
           <t>GHK_954_1445842097_2602600085249</t>
         </is>
       </c>
-      <c r="H257" s="4" t="n">
+      <c r="H257" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I257" t="n">
@@ -10456,10 +10453,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B258" s="3" t="n">
+      <c r="A258" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B258" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C258" t="inlineStr">
@@ -10487,7 +10484,7 @@
           <t>GHK_954_2460597079_2602600154310</t>
         </is>
       </c>
-      <c r="H258" s="4" t="n">
+      <c r="H258" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I258" t="n">
@@ -10495,10 +10492,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B259" s="3" t="n">
+      <c r="A259" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B259" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C259" t="inlineStr">
@@ -10526,7 +10523,7 @@
           <t>GHK_954_1535782252_2602600155753</t>
         </is>
       </c>
-      <c r="H259" s="4" t="n">
+      <c r="H259" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I259" t="n">
@@ -10534,10 +10531,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B260" s="3" t="n">
+      <c r="A260" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B260" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C260" t="inlineStr">
@@ -10565,7 +10562,7 @@
           <t>GHK_954_2518697459_2602300130536</t>
         </is>
       </c>
-      <c r="H260" s="4" t="n">
+      <c r="H260" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I260" t="n">
@@ -10573,10 +10570,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B261" s="3" t="n">
+      <c r="A261" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B261" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C261" t="inlineStr">
@@ -10604,7 +10601,7 @@
           <t>GHK_954_1506848454_2602300130624</t>
         </is>
       </c>
-      <c r="H261" s="4" t="n">
+      <c r="H261" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I261" t="n">
@@ -10612,10 +10609,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B262" s="3" t="n">
+      <c r="A262" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B262" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C262" t="inlineStr">
@@ -10643,7 +10640,7 @@
           <t>GHK_954_1019551090_2602300130951</t>
         </is>
       </c>
-      <c r="H262" s="4" t="n">
+      <c r="H262" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I262" t="n">
@@ -10651,10 +10648,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B263" s="3" t="n">
+      <c r="A263" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B263" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C263" t="inlineStr">
@@ -10682,7 +10679,7 @@
           <t>GHK_954_2518705559_2602400121051</t>
         </is>
       </c>
-      <c r="H263" s="4" t="n">
+      <c r="H263" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I263" t="n">
@@ -10690,10 +10687,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B264" s="3" t="n">
+      <c r="A264" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B264" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C264" t="inlineStr">
@@ -10721,7 +10718,7 @@
           <t>GHK_954_2518706540_2602400160241</t>
         </is>
       </c>
-      <c r="H264" s="4" t="n">
+      <c r="H264" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I264" t="n">
@@ -10729,10 +10726,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B265" s="3" t="n">
+      <c r="A265" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B265" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C265" t="inlineStr">
@@ -10760,7 +10757,7 @@
           <t>GHK_954_2518709643_2602500125239</t>
         </is>
       </c>
-      <c r="H265" s="4" t="n">
+      <c r="H265" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I265" t="n">
@@ -10768,10 +10765,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B266" s="3" t="n">
+      <c r="A266" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B266" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C266" t="inlineStr">
@@ -10799,7 +10796,7 @@
           <t>GHK_954_0251949277_2602600111756</t>
         </is>
       </c>
-      <c r="H266" s="4" t="n">
+      <c r="H266" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I266" t="n">
@@ -10807,10 +10804,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B267" s="3" t="n">
+      <c r="A267" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B267" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C267" t="inlineStr">
@@ -10838,7 +10835,7 @@
           <t>GHK_954_2384898306_2602500204239</t>
         </is>
       </c>
-      <c r="H267" s="4" t="n">
+      <c r="H267" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I267" t="n">
@@ -10846,10 +10843,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B268" s="3" t="n">
+      <c r="A268" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B268" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C268" t="inlineStr">
@@ -10877,7 +10874,7 @@
           <t>GHK_954_2518717596_2602600011909</t>
         </is>
       </c>
-      <c r="H268" s="4" t="n">
+      <c r="H268" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I268" t="n">
@@ -10885,10 +10882,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B269" s="3" t="n">
+      <c r="A269" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B269" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C269" t="inlineStr">
@@ -10916,7 +10913,7 @@
           <t>GHK_954_1558908776_2602600153246</t>
         </is>
       </c>
-      <c r="H269" s="4" t="n">
+      <c r="H269" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I269" t="n">
@@ -10924,10 +10921,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B270" s="3" t="n">
+      <c r="A270" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B270" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C270" t="inlineStr">
@@ -10955,7 +10952,7 @@
           <t>GHK_954_2518707464_2602600175249</t>
         </is>
       </c>
-      <c r="H270" s="4" t="n">
+      <c r="H270" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I270" t="n">
@@ -10963,10 +10960,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B271" s="3" t="n">
+      <c r="A271" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B271" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C271" t="inlineStr">
@@ -10994,7 +10991,7 @@
           <t>GHK_954_0227981511_2602300130912</t>
         </is>
       </c>
-      <c r="H271" s="4" t="n">
+      <c r="H271" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I271" t="n">
@@ -11002,10 +10999,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B272" s="3" t="n">
+      <c r="A272" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B272" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C272" t="inlineStr">
@@ -11033,7 +11030,7 @@
           <t>GHK_954_1561013580_2602500133047</t>
         </is>
       </c>
-      <c r="H272" s="4" t="n">
+      <c r="H272" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I272" t="n">
@@ -11041,10 +11038,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B273" s="3" t="n">
+      <c r="A273" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B273" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C273" t="inlineStr">
@@ -11072,7 +11069,7 @@
           <t>GHK_954_1075548345_2602400122240</t>
         </is>
       </c>
-      <c r="H273" s="4" t="n">
+      <c r="H273" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I273" t="n">
@@ -11080,10 +11077,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B274" s="3" t="n">
+      <c r="A274" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B274" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C274" t="inlineStr">
@@ -11111,7 +11108,7 @@
           <t>GHK_954_2518717299_2602500193259</t>
         </is>
       </c>
-      <c r="H274" s="4" t="n">
+      <c r="H274" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I274" t="n">
@@ -11119,10 +11116,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B275" s="3" t="n">
+      <c r="A275" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B275" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="C275" t="inlineStr">
@@ -11150,7 +11147,7 @@
           <t>GHK_954_2518719238_2602600085253</t>
         </is>
       </c>
-      <c r="H275" s="4" t="n">
+      <c r="H275" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="I275" t="n">
